--- a/sepsis_project - Students Version/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/ddqn_ppo_results.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDQN Pareto" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPO Pareto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDQN Trials" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPO Trials" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noise Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Analysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Analysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Overall Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DDQN Pareto" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PPO Pareto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DDQN Trials" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PPO Trials" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Noise Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Missing Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Event Analysis" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5617217499999999</v>
+        <v>0.5603718</v>
       </c>
       <c r="C2" t="n">
-        <v>0.65454</v>
+        <v>0.65312</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6009</v>
+        <v>0.6357</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D3" t="n">
         <v>50000</v>
@@ -512,7 +512,7 @@
         <v>100000</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.644</v>
+        <v>0.6314</v>
       </c>
       <c r="C4" t="n">
-        <v>0.67</v>
+        <v>0.674</v>
       </c>
       <c r="D4" t="n">
         <v>50000</v>
@@ -609,34 +609,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.732</v>
+        <v>0.728</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6415150000000001</v>
+        <v>0.6655350000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000267775333103133</v>
+        <v>0.0001073886382247958</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
         <v>0.05</v>
       </c>
       <c r="G2" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
         <v>100000</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,13 +717,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.714</v>
+        <v>0.716</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6570900000000001</v>
+        <v>0.6555799999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001090049253729382</v>
+        <v>0.0003574712922600246</v>
       </c>
       <c r="D2" t="n">
         <v>0.9</v>
@@ -732,24 +732,62 @@
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>512</v>
       </c>
       <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K2" t="n">
+        <v>64</v>
+      </c>
+      <c r="L2" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6570900000000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0001090049253729382</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>512</v>
+      </c>
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="J2" t="n">
-        <v>256</v>
-      </c>
-      <c r="K2" t="n">
-        <v>128</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="J3" t="n">
+        <v>256</v>
+      </c>
+      <c r="K3" t="n">
+        <v>128</v>
+      </c>
+      <c r="L3" t="n">
         <v>128</v>
       </c>
     </row>
@@ -821,42 +859,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000267775333103133</v>
+        <v>0.0001073886382247958</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D2" t="n">
         <v>0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
         <v>100000</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.732</v>
+        <v>0.728</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6415150000000001</v>
+        <v>0.6655350000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0008775452610882307</v>
+        <v>0.002249198965267357</v>
       </c>
       <c r="C3" t="n">
         <v>0.05</v>
@@ -865,54 +903,54 @@
         <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
         <v>10000</v>
       </c>
       <c r="G3" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.698</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6303650000000001</v>
+        <v>0.6334350000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0008556226023737445</v>
+        <v>0.001793348639944684</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="G4" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.696</v>
+        <v>0.678</v>
       </c>
       <c r="J4" t="n">
-        <v>0.611435</v>
+        <v>0.61826</v>
       </c>
     </row>
     <row r="5">
@@ -920,51 +958,51 @@
         <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0001073886382247958</v>
+        <v>0.0003617355603250917</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.597415</v>
+        <v>0.5912350000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0003617355603250917</v>
+        <v>0.0001423638128723575</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
         <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -973,82 +1011,82 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.668</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6112000000000001</v>
+        <v>0.58884</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0008289395383720047</v>
+        <v>0.001040166367988732</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
         <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.68</v>
+        <v>0.666</v>
       </c>
       <c r="J7" t="n">
-        <v>0.59111</v>
+        <v>0.60636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0001423638128723575</v>
+        <v>0.0008775452610882307</v>
       </c>
       <c r="C8" t="n">
         <v>0.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F8" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.68</v>
+        <v>0.666</v>
       </c>
       <c r="J8" t="n">
-        <v>0.58221</v>
+        <v>0.5899449999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002249198965267357</v>
+        <v>0.0003793280795162164</v>
       </c>
       <c r="C9" t="n">
         <v>0.05</v>
@@ -1057,22 +1095,22 @@
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.678</v>
+        <v>0.664</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6070050000000001</v>
+        <v>0.59236</v>
       </c>
     </row>
     <row r="10">
@@ -1080,71 +1118,71 @@
         <v>256</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0002183935292318299</v>
+        <v>0.003894923038838411</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
         <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G10" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.676</v>
+        <v>0.662</v>
       </c>
       <c r="J10" t="n">
-        <v>0.594685</v>
+        <v>0.59551</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="B11" t="n">
-        <v>0.003284210350911732</v>
+        <v>0.0002183935292318299</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G11" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.67</v>
+        <v>0.662</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6179049999999999</v>
+        <v>0.5708150000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003894923038838411</v>
+        <v>0.000267775333103133</v>
       </c>
       <c r="C12" t="n">
         <v>0.05</v>
@@ -1153,22 +1191,22 @@
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F12" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G12" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6052249999999999</v>
+        <v>0.573815</v>
       </c>
     </row>
     <row r="13">
@@ -1176,48 +1214,48 @@
         <v>64</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0001393595487688128</v>
+        <v>0.0001021837675800809</v>
       </c>
       <c r="C13" t="n">
         <v>0.05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
         <v>10000</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.668</v>
+        <v>0.656</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5999100000000001</v>
+        <v>0.586185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0001021837675800809</v>
+        <v>0.0004329677966181864</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
         <v>10000</v>
@@ -1226,45 +1264,45 @@
         <v>500</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.664</v>
+        <v>0.652</v>
       </c>
       <c r="J14" t="n">
-        <v>0.58724</v>
+        <v>0.5781600000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001040166367988732</v>
+        <v>0.0002060924941320236</v>
       </c>
       <c r="C15" t="n">
         <v>0.05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
         <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.66</v>
+        <v>0.652</v>
       </c>
       <c r="J15" t="n">
-        <v>0.593585</v>
+        <v>0.5755400000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1293,18 +1331,18 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="J16" t="n">
-        <v>0.578865</v>
+        <v>0.566975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0004329677966181864</v>
+        <v>0.003284210350911732</v>
       </c>
       <c r="C17" t="n">
         <v>0.2</v>
@@ -1313,62 +1351,62 @@
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F17" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="G17" t="n">
         <v>500</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>0.656</v>
+        <v>0.65</v>
       </c>
       <c r="J17" t="n">
-        <v>0.573175</v>
+        <v>0.526635</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0003793280795162164</v>
+        <v>0.0006867090776580455</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D18" t="n">
         <v>0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G18" t="n">
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.65</v>
+        <v>0.644</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5717850000000001</v>
+        <v>0.5792350000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0002060924941320236</v>
+        <v>0.0001393595487688128</v>
       </c>
       <c r="C19" t="n">
         <v>0.05</v>
@@ -1377,86 +1415,86 @@
         <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.648</v>
+        <v>0.636</v>
       </c>
       <c r="J19" t="n">
-        <v>0.563585</v>
+        <v>0.574345</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0006867090776580455</v>
+        <v>0.0008289395383720047</v>
       </c>
       <c r="C20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.05</v>
-      </c>
       <c r="E20" t="n">
         <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H20" t="n">
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>0.648</v>
+        <v>0.626</v>
       </c>
       <c r="J20" t="n">
-        <v>0.54827</v>
+        <v>0.5290049999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001793348639944684</v>
+        <v>0.0008556226023737445</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F21" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="G21" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.646</v>
+        <v>0.614</v>
       </c>
       <c r="J21" t="n">
-        <v>0.579495</v>
+        <v>0.53428</v>
       </c>
     </row>
   </sheetData>
@@ -1537,7 +1575,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0001090049253729382</v>
+        <v>0.0003574712922600246</v>
       </c>
       <c r="B2" t="n">
         <v>0.9</v>
@@ -1546,92 +1584,92 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>512</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="I2" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J2" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="K2" t="n">
-        <v>0.714</v>
+        <v>0.716</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6570900000000001</v>
+        <v>0.6555799999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002190714227215282</v>
+        <v>0.0001090049253729382</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="I3" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="J3" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="K3" t="n">
-        <v>0.696</v>
+        <v>0.714</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6093699999999999</v>
+        <v>0.6570900000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0005016631968599064</v>
+        <v>0.0004135867955263891</v>
       </c>
       <c r="B4" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
         <v>64</v>
@@ -1640,36 +1678,36 @@
         <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="L4" t="n">
-        <v>0.635455</v>
+        <v>0.61892</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0003574712922600246</v>
+        <v>0.0005016631968599064</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>64</v>
@@ -1678,74 +1716,74 @@
         <v>64</v>
       </c>
       <c r="J5" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.62287</v>
+        <v>0.635455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.002442046084491142</v>
+        <v>0.002190714227215282</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
         <v>64</v>
       </c>
       <c r="I6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="J6" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.59914</v>
+        <v>0.58994</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0009836162684900027</v>
+        <v>0.002904665979638735</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>128</v>
@@ -1757,10 +1795,10 @@
         <v>128</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5915750000000001</v>
+        <v>0.5972799999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1803,40 +1841,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002904665979638735</v>
+        <v>0.002322119672134761</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="I9" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="J9" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="K9" t="n">
         <v>0.678</v>
       </c>
       <c r="L9" t="n">
-        <v>0.606115</v>
+        <v>0.60883</v>
       </c>
     </row>
     <row r="10">
@@ -1955,28 +1993,28 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0004135867955263891</v>
+        <v>0.0008099164993582627</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C13" t="n">
         <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="G13" t="n">
         <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="I13" t="n">
         <v>64</v>
@@ -1985,18 +2023,18 @@
         <v>128</v>
       </c>
       <c r="K13" t="n">
-        <v>0.668</v>
+        <v>0.67</v>
       </c>
       <c r="L13" t="n">
-        <v>0.577765</v>
+        <v>0.604865</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002322119672134761</v>
+        <v>0.002458429052828939</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C14" t="n">
         <v>0.1</v>
@@ -2005,16 +2043,16 @@
         <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="I14" t="n">
         <v>128</v>
@@ -2026,27 +2064,27 @@
         <v>0.664</v>
       </c>
       <c r="L14" t="n">
-        <v>0.600715</v>
+        <v>0.5836950000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.002458429052828939</v>
+        <v>0.0003571439909823144</v>
       </c>
       <c r="B15" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0.1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
@@ -2055,62 +2093,62 @@
         <v>256</v>
       </c>
       <c r="I15" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="J15" t="n">
         <v>256</v>
       </c>
       <c r="K15" t="n">
-        <v>0.664</v>
+        <v>0.648</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5836950000000001</v>
+        <v>0.58956</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0008099164993582627</v>
+        <v>0.0009836162684900027</v>
       </c>
       <c r="B16" t="n">
         <v>0.9</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="G16" t="n">
         <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="I16" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="J16" t="n">
         <v>128</v>
       </c>
       <c r="K16" t="n">
-        <v>0.662</v>
+        <v>0.648</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.558415</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0003571439909823144</v>
+        <v>0.0003384522041201141</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="C17" t="n">
         <v>0.1</v>
@@ -2119,33 +2157,33 @@
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="I17" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="J17" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="K17" t="n">
-        <v>0.648</v>
+        <v>0.646</v>
       </c>
       <c r="L17" t="n">
-        <v>0.58956</v>
+        <v>0.5768150000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0002139331892500008</v>
+        <v>0.002442046084491142</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -2154,7 +2192,7 @@
         <v>0.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E18" t="n">
         <v>0.5</v>
@@ -2169,33 +2207,33 @@
         <v>64</v>
       </c>
       <c r="I18" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J18" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="K18" t="n">
-        <v>0.64</v>
+        <v>0.644</v>
       </c>
       <c r="L18" t="n">
-        <v>0.599205</v>
+        <v>0.546925</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.0001942663440330811</v>
+        <v>0.0002139331892500008</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
         <v>1024</v>
@@ -2204,57 +2242,57 @@
         <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="I19" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="J19" t="n">
         <v>64</v>
       </c>
       <c r="K19" t="n">
-        <v>0.634</v>
+        <v>0.64</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6012900000000001</v>
+        <v>0.599205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.0003384522041201141</v>
+        <v>0.0001942663440330811</v>
       </c>
       <c r="B20" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
         <v>128</v>
       </c>
       <c r="I20" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="J20" t="n">
         <v>64</v>
       </c>
       <c r="K20" t="n">
-        <v>0.626</v>
+        <v>0.634</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5481549999999999</v>
+        <v>0.6012900000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2336,13 +2374,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.602185</v>
+        <v>0.5766199999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="D2" t="n">
-        <v>9.324</v>
+        <v>8.646000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2350,13 +2388,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5773400000000001</v>
+        <v>0.6330800000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.66</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>9.811999999999999</v>
+        <v>8.792</v>
       </c>
     </row>
     <row r="4">
@@ -2364,13 +2402,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.606115</v>
+        <v>0.6427550000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="D4" t="n">
-        <v>9.545999999999999</v>
+        <v>8.882</v>
       </c>
     </row>
     <row r="5">
@@ -2378,13 +2416,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.574755</v>
+        <v>0.6637550000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.654</v>
+        <v>0.716</v>
       </c>
       <c r="D5" t="n">
-        <v>9.26</v>
+        <v>8.678000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2392,13 +2430,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5856549999999999</v>
+        <v>0.640835</v>
       </c>
       <c r="C6" t="n">
-        <v>0.676</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>10.486</v>
+        <v>7.808</v>
       </c>
     </row>
   </sheetData>
@@ -2442,13 +2480,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5934349999999999</v>
+        <v>0.630565</v>
       </c>
       <c r="C2" t="n">
-        <v>0.672</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>9.496</v>
+        <v>8.412000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2456,13 +2494,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.58701</v>
+        <v>0.649245</v>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.702</v>
       </c>
       <c r="D3" t="n">
-        <v>9.938000000000001</v>
+        <v>8.676</v>
       </c>
     </row>
     <row r="4">
@@ -2470,13 +2508,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.606115</v>
+        <v>0.6427550000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="D4" t="n">
-        <v>9.545999999999999</v>
+        <v>8.882</v>
       </c>
     </row>
     <row r="5">
@@ -2484,13 +2522,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6255550000000001</v>
+        <v>0.5855750000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="D5" t="n">
-        <v>9.972</v>
+        <v>8.757999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2498,13 +2536,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.577645</v>
+        <v>0.619325</v>
       </c>
       <c r="C6" t="n">
-        <v>0.66</v>
+        <v>0.674</v>
       </c>
       <c r="D6" t="n">
-        <v>9.69</v>
+        <v>8.512</v>
       </c>
     </row>
   </sheetData>
@@ -2548,13 +2586,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6246700000000001</v>
+        <v>0.6751200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.718</v>
+        <v>0.73</v>
       </c>
       <c r="D2" t="n">
-        <v>10.82</v>
+        <v>8.692</v>
       </c>
     </row>
     <row r="3">
@@ -2562,13 +2600,13 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.58636</v>
+        <v>0.642845</v>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.696</v>
       </c>
       <c r="D3" t="n">
-        <v>9.832000000000001</v>
+        <v>8.622</v>
       </c>
     </row>
     <row r="4">
@@ -2576,13 +2614,13 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.606115</v>
+        <v>0.6427550000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="D4" t="n">
-        <v>9.545999999999999</v>
+        <v>8.882</v>
       </c>
     </row>
     <row r="5">
@@ -2590,13 +2628,13 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51484</v>
+        <v>0.586635</v>
       </c>
       <c r="C5" t="n">
-        <v>0.58</v>
+        <v>0.636</v>
       </c>
       <c r="D5" t="n">
-        <v>7.738</v>
+        <v>8.416</v>
       </c>
     </row>
     <row r="6">
@@ -2604,13 +2642,13 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.441815</v>
+        <v>0.50745</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>0.544</v>
       </c>
       <c r="D6" t="n">
-        <v>7.09</v>
+        <v>6.064</v>
       </c>
     </row>
   </sheetData>

--- a/sepsis_project - Students Version/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/ddqn_ppo_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,20 +448,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Mean Return Std</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Survival Rate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Rate Std</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Episode Length</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Episode Length Std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Training Episodes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Eval Seeds</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Eval Episodes / Seed</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>buffer_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>target_update_freq</t>
         </is>
@@ -474,20 +504,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5603718</v>
+        <v>0.55919143</v>
       </c>
       <c r="C2" t="n">
-        <v>0.65312</v>
+        <v>0.003209781500857955</v>
       </c>
       <c r="D2" t="n">
+        <v>0.651756</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00300923246027951</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.340984000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.04253762428721183</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -500,19 +548,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6357</v>
+        <v>0.58812675</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.00177705740199916</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6670119999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.001571725166815125</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.764848000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.04532021756346714</v>
+      </c>
+      <c r="H3" t="n">
         <v>50000</v>
       </c>
-      <c r="E3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>100</v>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -522,20 +588,38 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6314</v>
+        <v>0.6612539999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.674</v>
+        <v>0.002663838947365217</v>
       </c>
       <c r="D4" t="n">
+        <v>0.6753279999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.002700614744831261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.852116000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0245460033406661</v>
+      </c>
+      <c r="H4" t="n">
         <v>50000</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>N/A (on-policy)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>N/A (on-policy)</t>
         </is>
@@ -552,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,45 +647,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>mean_return</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_arch</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>exploration_fraction</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>epsilon_min</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>buffer_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>target_update_freq</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>gradient_steps</t>
         </is>
@@ -609,34 +703,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.728</v>
+        <v>0.6744600000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6655350000000001</v>
+        <v>0.002673574386472148</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>0.6134486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001073886382247958</v>
+        <v>0.002617662265743974</v>
       </c>
       <c r="E2" t="n">
+        <v>256</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.001793348639944684</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32</v>
-      </c>
       <c r="H2" t="n">
-        <v>100000</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>50000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>250</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,55 +761,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>mean_return</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gae_lambda</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>clip_eps</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>entropy_coef</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>value_coef</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rollout_length</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>update_epochs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>minibatch_size</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hidden1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
         </is>
@@ -717,78 +827,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.716</v>
+        <v>0.6710199999999999</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6555799999999999</v>
+        <v>0.004289172414347559</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003574712922600246</v>
+        <v>0.6403731</v>
       </c>
       <c r="D2" t="n">
+        <v>0.004279511598155791</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0001942663440330811</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.9</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>512</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
       <c r="J2" t="n">
-        <v>64</v>
+        <v>1024</v>
       </c>
       <c r="K2" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
+        <v>128</v>
+      </c>
+      <c r="M2" t="n">
         <v>256</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.6570900000000001</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0001090049253729382</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>512</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>256</v>
-      </c>
-      <c r="K3" t="n">
-        <v>128</v>
-      </c>
-      <c r="L3" t="n">
-        <v>128</v>
+      <c r="N2" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -802,699 +880,829 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>net_arch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>exploration_fraction</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>epsilon_min</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>buffer_size</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>target_update_freq</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>gradient_steps</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>survival_rate</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>mean_return</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>0.6744600000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0001073886382247958</v>
+        <v>0.002673574386472148</v>
       </c>
       <c r="C2" t="n">
+        <v>0.6134486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.002617662265743974</v>
+      </c>
+      <c r="E2" t="n">
+        <v>256</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.001793348639944684</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.1</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>100</v>
-      </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.728</v>
+        <v>64</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6655350000000001</v>
+        <v>50000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>250</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64</v>
+        <v>0.66966</v>
       </c>
       <c r="B3" t="n">
+        <v>0.004981264899601303</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6109927000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.005148260083513655</v>
+      </c>
+      <c r="E3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.002249198965267357</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E3" t="n">
-        <v>64</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J3" t="n">
         <v>10000</v>
       </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
         <v>50</v>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6334350000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>256</v>
+        <v>0.66788</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001793348639944684</v>
+        <v>0.0029911536236041</v>
       </c>
       <c r="C4" t="n">
+        <v>0.5879402</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.003563220056178117</v>
+      </c>
+      <c r="E4" t="n">
+        <v>128</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0001423638128723575</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.1</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>64</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>250</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
+        <v>64</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.61826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>0.6671400000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0003617355603250917</v>
+        <v>0.003808936859544928</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2</v>
+        <v>0.57530995</v>
       </c>
       <c r="D5" t="n">
+        <v>0.003858917138427599</v>
+      </c>
+      <c r="E5" t="n">
+        <v>256</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0002183935292318299</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.01</v>
       </c>
-      <c r="E5" t="n">
-        <v>64</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.678</v>
+        <v>64</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5912350000000001</v>
+        <v>100000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>250</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128</v>
+        <v>0.6652600000000001</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0001423638128723575</v>
+        <v>0.007100563357931526</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05</v>
+        <v>0.60396075</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>0.00681814933422188</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F6" t="n">
-        <v>100000</v>
+        <v>0.001040166367988732</v>
       </c>
       <c r="G6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" t="n">
+        <v>64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K6" t="n">
         <v>100</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.58884</v>
+      <c r="L6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128</v>
+        <v>0.6648800000000001</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001040166367988732</v>
+        <v>0.007780552679598035</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05</v>
+        <v>0.5915883</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.008047677705400456</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F7" t="n">
+        <v>0.0008775452610882307</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>128</v>
+      </c>
+      <c r="J7" t="n">
         <v>10000</v>
       </c>
-      <c r="G7" t="n">
-        <v>100</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
+        <v>500</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.60636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>256</v>
+        <v>0.66476</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0008775452610882307</v>
+        <v>0.00266889490238939</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05</v>
+        <v>0.60005545</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0.002835583534521576</v>
       </c>
       <c r="E8" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>10000</v>
+        <v>0.0001073886382247958</v>
       </c>
       <c r="G8" t="n">
-        <v>500</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.666</v>
+        <v>32</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5899449999999999</v>
+        <v>100000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>256</v>
+        <v>0.66296</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0003793280795162164</v>
+        <v>0.003548661719578239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05</v>
+        <v>0.5804783</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>0.003085278058781738</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>50000</v>
+        <v>0.0003617355603250917</v>
       </c>
       <c r="G9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>64</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K9" t="n">
         <v>100</v>
       </c>
-      <c r="H9" t="n">
+      <c r="L9" t="n">
         <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.59236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>0.66284</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00223450218169507</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.58655055</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.00259342561465525</v>
+      </c>
+      <c r="E10" t="n">
         <v>256</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.003894923038838411</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E10" t="n">
-        <v>64</v>
-      </c>
       <c r="F10" t="n">
+        <v>0.0003793280795162164</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J10" t="n">
         <v>50000</v>
       </c>
-      <c r="G10" t="n">
-        <v>500</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.59551</v>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>0.6620199999999999</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.005216512244785781</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5922547</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005291413422942861</v>
+      </c>
+      <c r="E11" t="n">
         <v>256</v>
       </c>
-      <c r="B11" t="n">
-        <v>0.0002183935292318299</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E11" t="n">
-        <v>64</v>
-      </c>
       <c r="F11" t="n">
-        <v>100000</v>
+        <v>0.003894923038838411</v>
       </c>
       <c r="G11" t="n">
-        <v>250</v>
+        <v>0.05</v>
       </c>
       <c r="H11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>64</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>500</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5708150000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128</v>
+        <v>0.66112</v>
       </c>
       <c r="B12" t="n">
-        <v>0.000267775333103133</v>
+        <v>0.005944072677886758</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05</v>
+        <v>0.595909</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.00532078881311311</v>
       </c>
       <c r="E12" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>100000</v>
+        <v>0.0001393595487688128</v>
       </c>
       <c r="G12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K12" t="n">
         <v>50</v>
       </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.573815</v>
+      <c r="L12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>64</v>
+        <v>0.6606</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0001021837675800809</v>
+        <v>0.003293933818400104</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05</v>
+        <v>0.58632035</v>
       </c>
       <c r="D13" t="n">
+        <v>0.003761535348099236</v>
+      </c>
+      <c r="E13" t="n">
+        <v>128</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0004329677966181864</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.01</v>
       </c>
-      <c r="E13" t="n">
-        <v>64</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
+        <v>32</v>
+      </c>
+      <c r="J13" t="n">
         <v>10000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="K13" t="n">
         <v>500</v>
       </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.586185</v>
+      <c r="L13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128</v>
+        <v>0.66008</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0004329677966181864</v>
+        <v>0.002101666005815367</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2</v>
+        <v>0.5806394000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.002230560079610025</v>
       </c>
       <c r="E14" t="n">
-        <v>32</v>
+        <v>256</v>
       </c>
       <c r="F14" t="n">
-        <v>10000</v>
+        <v>0.0006901506581791928</v>
       </c>
       <c r="G14" t="n">
-        <v>500</v>
+        <v>0.05</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.652</v>
+        <v>128</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5781600000000001</v>
+        <v>100000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>250</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>256</v>
+        <v>0.6595</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0002060924941320236</v>
+        <v>0.002028546277510083</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05</v>
+        <v>0.5844917000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>0.002125967657620858</v>
       </c>
       <c r="E15" t="n">
         <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>50000</v>
+        <v>0.0001021837675800809</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>0.05</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.652</v>
+        <v>64</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5755400000000001</v>
+        <v>10000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>0.6589600000000001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.008211150954646961</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5712496</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.007556233557881233</v>
+      </c>
+      <c r="E16" t="n">
         <v>256</v>
       </c>
-      <c r="B16" t="n">
-        <v>0.0006901506581791928</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
+        <v>0.0008289395383720047</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.1</v>
       </c>
-      <c r="E16" t="n">
-        <v>128</v>
-      </c>
-      <c r="F16" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G16" t="n">
-        <v>250</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
-        <v>0.65</v>
+        <v>64</v>
       </c>
       <c r="J16" t="n">
-        <v>0.566975</v>
+        <v>50000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>50</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>64</v>
+        <v>0.6582600000000001</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003284210350911732</v>
+        <v>0.005444079352838296</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2</v>
+        <v>0.5755668</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>0.006416742084675845</v>
       </c>
       <c r="E17" t="n">
         <v>128</v>
       </c>
       <c r="F17" t="n">
-        <v>50000</v>
+        <v>0.000267775333103133</v>
       </c>
       <c r="G17" t="n">
-        <v>500</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.65</v>
+        <v>128</v>
       </c>
       <c r="J17" t="n">
-        <v>0.526635</v>
+        <v>100000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>50</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>64</v>
+        <v>0.65776</v>
       </c>
       <c r="B18" t="n">
+        <v>0.004408287649416698</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5937209999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.004572825600080349</v>
+      </c>
+      <c r="E18" t="n">
+        <v>64</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.0006867090776580455</v>
       </c>
-      <c r="C18" t="n">
+      <c r="G18" t="n">
         <v>0.1</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E18" t="n">
-        <v>64</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I18" t="n">
+        <v>64</v>
+      </c>
+      <c r="J18" t="n">
         <v>100000</v>
       </c>
-      <c r="G18" t="n">
+      <c r="K18" t="n">
         <v>100</v>
       </c>
-      <c r="H18" t="n">
+      <c r="L18" t="n">
         <v>4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.5792350000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>64</v>
+        <v>0.65618</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0001393595487688128</v>
+        <v>0.003346191865389678</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05</v>
+        <v>0.54121025</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1</v>
+        <v>0.002948062276733678</v>
       </c>
       <c r="E19" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>10000</v>
+        <v>0.003284210350911732</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.636</v>
+        <v>128</v>
       </c>
       <c r="J19" t="n">
-        <v>0.574345</v>
+        <v>50000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>500</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.003071970051937368</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5750618</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.003429470382763221</v>
+      </c>
+      <c r="E20" t="n">
         <v>256</v>
       </c>
-      <c r="B20" t="n">
-        <v>0.0008289395383720047</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
+        <v>0.0002060924941320236</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.1</v>
       </c>
-      <c r="E20" t="n">
-        <v>64</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="I20" t="n">
+        <v>64</v>
+      </c>
+      <c r="J20" t="n">
         <v>50000</v>
       </c>
-      <c r="G20" t="n">
+      <c r="K20" t="n">
         <v>50</v>
       </c>
-      <c r="H20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5290049999999999</v>
+      <c r="L20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>64</v>
+        <v>0.65068</v>
       </c>
       <c r="B21" t="n">
+        <v>0.004131827682757324</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5656667499999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.004418571272906001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>64</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.0008556226023737445</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="G21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.01</v>
       </c>
-      <c r="E21" t="n">
-        <v>128</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
+        <v>128</v>
+      </c>
+      <c r="J21" t="n">
         <v>10000</v>
       </c>
-      <c r="G21" t="n">
+      <c r="K21" t="n">
         <v>500</v>
       </c>
-      <c r="H21" t="n">
+      <c r="L21" t="n">
         <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.53428</v>
       </c>
     </row>
   </sheetData>
@@ -1508,829 +1716,959 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gae_lambda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>clip_eps</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>entropy_coef</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>value_coef</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rollout_length</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>update_epochs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>minibatch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hidden1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>survival_rate</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mean_return</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0003574712922600246</v>
+        <v>0.6710199999999999</v>
       </c>
       <c r="B2" t="n">
+        <v>0.004289172414347559</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6403731</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.004279511598155791</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0001942663440330811</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.9</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
-        <v>512</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" t="n">
-        <v>64</v>
-      </c>
-      <c r="I2" t="n">
-        <v>64</v>
-      </c>
       <c r="J2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>128</v>
+      </c>
+      <c r="M2" t="n">
         <v>256</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.6555799999999999</v>
+      <c r="N2" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0.6704399999999999</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.004519181341791912</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6117704500000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.004731487128799963</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.0001090049253729382</v>
       </c>
-      <c r="B3" t="n">
+      <c r="F3" t="n">
         <v>0.9</v>
       </c>
-      <c r="C3" t="n">
+      <c r="G3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="J3" t="n">
         <v>512</v>
       </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="n">
         <v>256</v>
       </c>
-      <c r="I3" t="n">
-        <v>128</v>
-      </c>
-      <c r="J3" t="n">
-        <v>128</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.6570900000000001</v>
+      <c r="M3" t="n">
+        <v>128</v>
+      </c>
+      <c r="N3" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0004135867955263891</v>
+        <v>0.67034</v>
       </c>
       <c r="B4" t="n">
+        <v>0.003693643187964954</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6305271</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.003490899336131028</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0002139331892500008</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.5</v>
       </c>
-      <c r="F4" t="n">
-        <v>512</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>64</v>
-      </c>
-      <c r="I4" t="n">
-        <v>64</v>
-      </c>
       <c r="J4" t="n">
-        <v>128</v>
+        <v>1024</v>
       </c>
       <c r="K4" t="n">
-        <v>0.702</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.61892</v>
+        <v>64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>64</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>0.66784</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.003360505914293274</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6135873500000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.003734496027745891</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.0005016631968599064</v>
       </c>
-      <c r="B5" t="n">
+      <c r="F5" t="n">
         <v>0.95</v>
       </c>
-      <c r="C5" t="n">
+      <c r="G5" t="n">
         <v>0.2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="H5" t="n">
         <v>0.01</v>
       </c>
-      <c r="E5" t="n">
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>1024</v>
       </c>
-      <c r="G5" t="n">
+      <c r="K5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
-        <v>64</v>
-      </c>
-      <c r="I5" t="n">
-        <v>64</v>
-      </c>
-      <c r="J5" t="n">
-        <v>64</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.635455</v>
+        <v>64</v>
+      </c>
+      <c r="M5" t="n">
+        <v>64</v>
+      </c>
+      <c r="N5" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.002190714227215282</v>
+        <v>0.66554</v>
       </c>
       <c r="B6" t="n">
+        <v>0.005697631086688569</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.603576</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00579754870343926</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0003574712922600246</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>512</v>
+      </c>
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
-        <v>64</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>64</v>
+      </c>
+      <c r="M6" t="n">
+        <v>64</v>
+      </c>
+      <c r="N6" t="n">
         <v>256</v>
-      </c>
-      <c r="J6" t="n">
-        <v>64</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.6860000000000001</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.58994</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.002904665979638735</v>
+        <v>0.6654</v>
       </c>
       <c r="B7" t="n">
+        <v>0.005250238089839329</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5916872999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.005816727917717116</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0002710864828729778</v>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
+        <v>512</v>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
-        <v>128</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>256</v>
       </c>
-      <c r="J7" t="n">
-        <v>128</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5972799999999999</v>
+      <c r="M7" t="n">
+        <v>128</v>
+      </c>
+      <c r="N7" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0002710864828729778</v>
+        <v>0.6643600000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.008816632010013781</v>
       </c>
       <c r="C8" t="n">
+        <v>0.5983796000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.008579123302747769</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.002322119672134761</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>512</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
+      <c r="L8" t="n">
+        <v>64</v>
+      </c>
+      <c r="M8" t="n">
+        <v>128</v>
+      </c>
+      <c r="N8" t="n">
         <v>256</v>
-      </c>
-      <c r="I8" t="n">
-        <v>128</v>
-      </c>
-      <c r="J8" t="n">
-        <v>256</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.6042649999999998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002322119672134761</v>
+        <v>0.66106</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9</v>
+        <v>0.006753739704785792</v>
       </c>
       <c r="C9" t="n">
+        <v>0.6009727500000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.006823586655399806</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0003571439909823144</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
-        <v>64</v>
-      </c>
-      <c r="I9" t="n">
-        <v>128</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>256</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.60883</v>
+      <c r="M9" t="n">
+        <v>256</v>
+      </c>
+      <c r="N9" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0004872420129560896</v>
+        <v>0.6607200000000001</v>
       </c>
       <c r="B10" t="n">
+        <v>0.00224988888614525</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5797524000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001808292017001139</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0004135867955263891</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.5</v>
       </c>
-      <c r="F10" t="n">
+      <c r="J10" t="n">
         <v>512</v>
       </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>10</v>
       </c>
-      <c r="H10" t="n">
-        <v>256</v>
-      </c>
-      <c r="I10" t="n">
-        <v>256</v>
-      </c>
-      <c r="J10" t="n">
-        <v>128</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.678</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.5858949999999999</v>
+        <v>64</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64</v>
+      </c>
+      <c r="N10" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0001017364485544502</v>
+        <v>0.66042</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.001460136979875521</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3</v>
+        <v>0.589828</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>0.00253930730589076</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.0001972161097057403</v>
       </c>
       <c r="F11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" t="n">
         <v>512</v>
       </c>
-      <c r="G11" t="n">
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="n">
-        <v>128</v>
-      </c>
-      <c r="I11" t="n">
-        <v>64</v>
-      </c>
-      <c r="J11" t="n">
-        <v>128</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.676</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.60956</v>
+        <v>64</v>
+      </c>
+      <c r="M11" t="n">
+        <v>256</v>
+      </c>
+      <c r="N11" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0004841041099321571</v>
+        <v>0.65938</v>
       </c>
       <c r="B12" t="n">
-        <v>0.95</v>
+        <v>0.00595961408146534</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2</v>
+        <v>0.5977151000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.006062735432542</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.0008099164993582627</v>
       </c>
       <c r="F12" t="n">
-        <v>2048</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
         <v>256</v>
       </c>
-      <c r="J12" t="n">
-        <v>128</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.5932999999999999</v>
+      <c r="M12" t="n">
+        <v>64</v>
+      </c>
+      <c r="N12" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0008099164993582627</v>
+        <v>0.65864</v>
       </c>
       <c r="B13" t="n">
+        <v>0.003908068576675706</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5731065999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.003664884085820468</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0009836162684900027</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.9</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1024</v>
-      </c>
       <c r="G13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K13" t="n">
         <v>10</v>
       </c>
-      <c r="H13" t="n">
+      <c r="L13" t="n">
+        <v>128</v>
+      </c>
+      <c r="M13" t="n">
         <v>256</v>
       </c>
-      <c r="I13" t="n">
-        <v>64</v>
-      </c>
-      <c r="J13" t="n">
-        <v>128</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.604865</v>
+      <c r="N13" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002458429052828939</v>
+        <v>0.6582999999999999</v>
       </c>
       <c r="B14" t="n">
-        <v>0.95</v>
+        <v>0.002469817807045685</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1</v>
+        <v>0.5925770499999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>0.002450955779129859</v>
       </c>
       <c r="E14" t="n">
+        <v>0.0001017364485544502</v>
+      </c>
+      <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
         <v>512</v>
       </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
-        <v>256</v>
-      </c>
-      <c r="I14" t="n">
-        <v>128</v>
-      </c>
-      <c r="J14" t="n">
-        <v>256</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.664</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.5836950000000001</v>
+        <v>128</v>
+      </c>
+      <c r="M14" t="n">
+        <v>64</v>
+      </c>
+      <c r="N14" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0003571439909823144</v>
+        <v>0.65816</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0.00359485743806343</v>
       </c>
       <c r="C15" t="n">
+        <v>0.5887751</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.004061269642919573</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0003384522041201141</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.1</v>
       </c>
-      <c r="D15" t="n">
+      <c r="H15" t="n">
         <v>0.01</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>256</v>
-      </c>
       <c r="I15" t="n">
-        <v>256</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>256</v>
+        <v>2048</v>
       </c>
       <c r="K15" t="n">
-        <v>0.648</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>0.58956</v>
+        <v>128</v>
+      </c>
+      <c r="M15" t="n">
+        <v>128</v>
+      </c>
+      <c r="N15" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0009836162684900027</v>
+        <v>0.6575399999999999</v>
       </c>
       <c r="B16" t="n">
-        <v>0.9</v>
+        <v>0.006503306851133519</v>
       </c>
       <c r="C16" t="n">
+        <v>0.56382235</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.006760492788066577</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.002190714227215282</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.3</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
         <v>2048</v>
       </c>
-      <c r="G16" t="n">
+      <c r="K16" t="n">
         <v>10</v>
       </c>
-      <c r="H16" t="n">
-        <v>128</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
+        <v>64</v>
+      </c>
+      <c r="M16" t="n">
         <v>256</v>
       </c>
-      <c r="J16" t="n">
-        <v>128</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.558415</v>
+      <c r="N16" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0003384522041201141</v>
+        <v>0.65586</v>
       </c>
       <c r="B17" t="n">
+        <v>0.002910841802640583</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.58271035</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.003388411056454054</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0004841041099321571</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.95</v>
       </c>
-      <c r="C17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.5</v>
       </c>
-      <c r="F17" t="n">
+      <c r="J17" t="n">
         <v>2048</v>
       </c>
-      <c r="G17" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" t="n">
-        <v>128</v>
-      </c>
-      <c r="I17" t="n">
-        <v>128</v>
-      </c>
-      <c r="J17" t="n">
-        <v>64</v>
-      </c>
       <c r="K17" t="n">
-        <v>0.646</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5768150000000001</v>
+        <v>128</v>
+      </c>
+      <c r="M17" t="n">
+        <v>256</v>
+      </c>
+      <c r="N17" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.002442046084491142</v>
+        <v>0.6548</v>
       </c>
       <c r="B18" t="n">
+        <v>0.002434132288927602</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5642702000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.002061406470713636</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0004872420129560896</v>
+      </c>
+      <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.5</v>
       </c>
-      <c r="F18" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>64</v>
-      </c>
-      <c r="I18" t="n">
-        <v>128</v>
-      </c>
       <c r="J18" t="n">
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="K18" t="n">
-        <v>0.644</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>0.546925</v>
+        <v>256</v>
+      </c>
+      <c r="M18" t="n">
+        <v>256</v>
+      </c>
+      <c r="N18" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.0002139331892500008</v>
+        <v>0.65364</v>
       </c>
       <c r="B19" t="n">
+        <v>0.002374447304111025</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5672216000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0027174213742075</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.002904665979638735</v>
+      </c>
+      <c r="F19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="n">
+      <c r="G19" t="n">
         <v>0.2</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
         <v>1024</v>
       </c>
-      <c r="G19" t="n">
+      <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="H19" t="n">
-        <v>64</v>
-      </c>
-      <c r="I19" t="n">
-        <v>64</v>
-      </c>
-      <c r="J19" t="n">
-        <v>64</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.64</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.599205</v>
+        <v>128</v>
+      </c>
+      <c r="M19" t="n">
+        <v>256</v>
+      </c>
+      <c r="N19" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.0001942663440330811</v>
+        <v>0.65108</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9</v>
+        <v>0.003535109616405126</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3</v>
+        <v>0.5578465499999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.003750391768702331</v>
       </c>
       <c r="E20" t="n">
+        <v>0.002442046084491142</v>
+      </c>
+      <c r="F20" t="n">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J20" t="n">
         <v>1024</v>
       </c>
-      <c r="G20" t="n">
+      <c r="K20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
-        <v>128</v>
-      </c>
-      <c r="I20" t="n">
-        <v>256</v>
-      </c>
-      <c r="J20" t="n">
-        <v>64</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.634</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.6012900000000001</v>
+        <v>64</v>
+      </c>
+      <c r="M20" t="n">
+        <v>128</v>
+      </c>
+      <c r="N20" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.0001972161097057403</v>
+        <v>0.65038</v>
       </c>
       <c r="B21" t="n">
+        <v>0.004649408564538066</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5759699</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.004243689707229974</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.002458429052828939</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.95</v>
       </c>
-      <c r="C21" t="n">
+      <c r="G21" t="n">
         <v>0.1</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
         <v>512</v>
       </c>
-      <c r="G21" t="n">
+      <c r="K21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
-        <v>64</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>256</v>
       </c>
-      <c r="J21" t="n">
-        <v>128</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.55403</v>
+      <c r="M21" t="n">
+        <v>128</v>
+      </c>
+      <c r="N21" t="n">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2374,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5766199999999999</v>
+        <v>0.6604549999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.674</v>
       </c>
       <c r="D2" t="n">
-        <v>8.646000000000001</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="3">
@@ -2388,13 +2726,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6330800000000001</v>
+        <v>0.69631</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="D3" t="n">
-        <v>8.792</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="4">
@@ -2402,13 +2740,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6427550000000001</v>
+        <v>0.67675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.698</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>8.882</v>
+        <v>8.173999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2416,13 +2754,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6637550000000001</v>
+        <v>0.6855450000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.716</v>
+        <v>0.698</v>
       </c>
       <c r="D5" t="n">
-        <v>8.678000000000001</v>
+        <v>7.632</v>
       </c>
     </row>
     <row r="6">
@@ -2430,13 +2768,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.640835</v>
+        <v>0.67395</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>7.808</v>
+        <v>7.734</v>
       </c>
     </row>
   </sheetData>
@@ -2480,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.630565</v>
+        <v>0.677465</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>8.412000000000001</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="3">
@@ -2494,13 +2832,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.649245</v>
+        <v>0.6490050000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.702</v>
+        <v>0.664</v>
       </c>
       <c r="D3" t="n">
-        <v>8.676</v>
+        <v>7.954</v>
       </c>
     </row>
     <row r="4">
@@ -2508,13 +2846,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6427550000000001</v>
+        <v>0.67675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.698</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>8.882</v>
+        <v>8.173999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2522,13 +2860,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5855750000000001</v>
+        <v>0.6402</v>
       </c>
       <c r="C5" t="n">
-        <v>0.64</v>
+        <v>0.654</v>
       </c>
       <c r="D5" t="n">
-        <v>8.757999999999999</v>
+        <v>7.688</v>
       </c>
     </row>
     <row r="6">
@@ -2536,13 +2874,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.619325</v>
+        <v>0.6636599999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.674</v>
+        <v>0.678</v>
       </c>
       <c r="D6" t="n">
-        <v>8.512</v>
+        <v>8.01</v>
       </c>
     </row>
   </sheetData>
@@ -2586,13 +2924,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6751200000000001</v>
+        <v>0.701065</v>
       </c>
       <c r="C2" t="n">
-        <v>0.73</v>
+        <v>0.716</v>
       </c>
       <c r="D2" t="n">
-        <v>8.692</v>
+        <v>8.554</v>
       </c>
     </row>
     <row r="3">
@@ -2600,13 +2938,13 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.642845</v>
+        <v>0.6368199999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.65</v>
       </c>
       <c r="D3" t="n">
-        <v>8.622</v>
+        <v>7.536</v>
       </c>
     </row>
     <row r="4">
@@ -2614,13 +2952,13 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6427550000000001</v>
+        <v>0.67675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.698</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>8.882</v>
+        <v>8.173999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2628,13 +2966,13 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.586635</v>
+        <v>0.5903400000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.636</v>
+        <v>0.604</v>
       </c>
       <c r="D5" t="n">
-        <v>8.416</v>
+        <v>7.282</v>
       </c>
     </row>
     <row r="6">
@@ -2642,13 +2980,13 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.50745</v>
+        <v>0.5021100000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.544</v>
+        <v>0.512</v>
       </c>
       <c r="D6" t="n">
-        <v>6.064</v>
+        <v>5.842</v>
       </c>
     </row>
   </sheetData>

--- a/sepsis_project - Students Version/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/ddqn_ppo_results.xlsx
@@ -463,12 +463,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Mean Episode Length</t>
+          <t>Mean Length</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mean Episode Length Std</t>
+          <t>Mean Length Std</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -504,22 +504,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.55919143</v>
+        <v>0.56001744</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003209781500857955</v>
+        <v>0.001585247698468581</v>
       </c>
       <c r="D2" t="n">
-        <v>0.651756</v>
+        <v>0.65262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00300923246027951</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9.340984000000001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.04253762428721183</v>
+        <v>0.001580822570689052</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -548,22 +552,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.58812675</v>
+        <v>0.5783678</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00177705740199916</v>
+        <v>0.001385522064512141</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6670119999999999</v>
+        <v>0.653272</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001571725166815125</v>
+        <v>0.001473268475193836</v>
       </c>
       <c r="F3" t="n">
-        <v>8.764848000000001</v>
+        <v>9.385484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04532021756346714</v>
+        <v>0.03496292436281628</v>
       </c>
       <c r="H3" t="n">
         <v>50000</v>
@@ -578,7 +582,7 @@
         <v>50000</v>
       </c>
       <c r="L3" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4">
@@ -636,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,40 +707,78 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6744600000000001</v>
+        <v>0.6679</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002673574386472148</v>
+        <v>0.006013734280794266</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6134486</v>
+        <v>0.6079471000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002617662265743974</v>
+        <v>0.006168559451464384</v>
       </c>
       <c r="E2" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001793348639944684</v>
+        <v>0.003284210350911732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J2" t="n">
         <v>50000</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.65678</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.004119101843848972</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.61581535</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.00403991542532144</v>
+      </c>
+      <c r="E3" t="n">
+        <v>256</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.003894923038838411</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>500</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -947,98 +989,98 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6744600000000001</v>
+        <v>0.6679</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002673574386472148</v>
+        <v>0.006013734280794266</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6134486</v>
+        <v>0.6079471000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002617662265743974</v>
+        <v>0.006168559451464384</v>
       </c>
       <c r="E2" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001793348639944684</v>
+        <v>0.003284210350911732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J2" t="n">
         <v>50000</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.66966</v>
+        <v>0.6633199999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004981264899601303</v>
+        <v>0.002139392437118537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6109927000000001</v>
+        <v>0.5954849</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005148260083513655</v>
+        <v>0.002012492116444211</v>
       </c>
       <c r="E3" t="n">
         <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002249198965267357</v>
+        <v>0.0001073886382247958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="n">
         <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.66788</v>
+        <v>0.65778</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0029911536236041</v>
+        <v>0.003160221511223521</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5879402</v>
+        <v>0.5735627</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003563220056178117</v>
+        <v>0.003127105137943045</v>
       </c>
       <c r="E4" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001423638128723575</v>
+        <v>0.0001393595487688128</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1047,30 +1089,30 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J4" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.6671400000000001</v>
+        <v>0.65766</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003808936859544928</v>
+        <v>0.00144499134945508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.57530995</v>
+        <v>0.5602282000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003858917138427599</v>
+        <v>0.001580217265520793</v>
       </c>
       <c r="E5" t="n">
         <v>256</v>
@@ -1099,60 +1141,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6652600000000001</v>
+        <v>0.65706</v>
       </c>
       <c r="B6" t="n">
-        <v>0.007100563357931526</v>
+        <v>0.003698378022863547</v>
       </c>
       <c r="C6" t="n">
-        <v>0.60396075</v>
+        <v>0.59224755</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00681814933422188</v>
+        <v>0.003494640053889656</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001040166367988732</v>
+        <v>0.0006867090776580455</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I6" t="n">
         <v>64</v>
       </c>
       <c r="J6" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K6" t="n">
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.6648800000000001</v>
+        <v>0.65678</v>
       </c>
       <c r="B7" t="n">
-        <v>0.007780552679598035</v>
+        <v>0.004119101843848972</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5915883</v>
+        <v>0.61581535</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008047677705400456</v>
+        <v>0.00403991542532144</v>
       </c>
       <c r="E7" t="n">
         <v>256</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008775452610882307</v>
+        <v>0.003894923038838411</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1161,10 +1203,10 @@
         <v>0.05</v>
       </c>
       <c r="I7" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J7" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="K7" t="n">
         <v>500</v>
@@ -1175,113 +1217,113 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.66476</v>
+        <v>0.65588</v>
       </c>
       <c r="B8" t="n">
-        <v>0.00266889490238939</v>
+        <v>0.005698859535029787</v>
       </c>
       <c r="C8" t="n">
-        <v>0.60005545</v>
+        <v>0.54010475</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002835583534521576</v>
+        <v>0.00602584477220829</v>
       </c>
       <c r="E8" t="n">
         <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001073886382247958</v>
+        <v>0.0003617355603250917</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J8" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K8" t="n">
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.66296</v>
+        <v>0.6545400000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003548661719578239</v>
+        <v>0.00240686518110176</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5804783</v>
+        <v>0.5623293</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003085278058781738</v>
+        <v>0.002882284724181499</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003617355603250917</v>
+        <v>0.0008775452610882307</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I9" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J9" t="n">
         <v>10000</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.66284</v>
+        <v>0.65438</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00223450218169507</v>
+        <v>0.005837550856309508</v>
       </c>
       <c r="C10" t="n">
-        <v>0.58655055</v>
+        <v>0.57569305</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00259342561465525</v>
+        <v>0.006186582741101909</v>
       </c>
       <c r="E10" t="n">
         <v>256</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0003793280795162164</v>
+        <v>0.0002060924941320236</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J10" t="n">
         <v>50000</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -1289,136 +1331,136 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.6620199999999999</v>
+        <v>0.65416</v>
       </c>
       <c r="B11" t="n">
-        <v>0.005216512244785781</v>
+        <v>0.001393915348936227</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5922547</v>
+        <v>0.57163995</v>
       </c>
       <c r="D11" t="n">
-        <v>0.005291413422942861</v>
+        <v>0.001670239947208199</v>
       </c>
       <c r="E11" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003894923038838411</v>
+        <v>0.0001021837675800809</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I11" t="n">
         <v>64</v>
       </c>
       <c r="J11" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="K11" t="n">
         <v>500</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.66112</v>
+        <v>0.65384</v>
       </c>
       <c r="B12" t="n">
-        <v>0.005944072677886758</v>
+        <v>0.004121650154974348</v>
       </c>
       <c r="C12" t="n">
-        <v>0.595909</v>
+        <v>0.5724329</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00532078881311311</v>
+        <v>0.004052790437618212</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0001393595487688128</v>
+        <v>0.0003793280795162164</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
         <v>32</v>
       </c>
       <c r="J12" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="K12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6606</v>
+        <v>0.6531</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003293933818400104</v>
+        <v>0.004848195540610958</v>
       </c>
       <c r="C13" t="n">
-        <v>0.58632035</v>
+        <v>0.5520993</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003761535348099236</v>
+        <v>0.00547510961191646</v>
       </c>
       <c r="E13" t="n">
         <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0004329677966181864</v>
+        <v>0.001040166367988732</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H13" t="n">
         <v>0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J13" t="n">
         <v>10000</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.66008</v>
+        <v>0.65266</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002101666005815367</v>
+        <v>0.008595231235981963</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5806394000000001</v>
+        <v>0.5775380999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002230560079610025</v>
+        <v>0.008555990380648554</v>
       </c>
       <c r="E14" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0006901506581791928</v>
+        <v>0.0001423638128723575</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1427,127 +1469,127 @@
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J14" t="n">
         <v>100000</v>
       </c>
       <c r="K14" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6595</v>
+        <v>0.6502800000000001</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002028546277510083</v>
+        <v>0.005965064961926255</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5844917000000001</v>
+        <v>0.55648105</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002125967657620858</v>
+        <v>0.005811125031996836</v>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0001021837675800809</v>
+        <v>0.000267775333103133</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J15" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K15" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6589600000000001</v>
+        <v>0.6501400000000001</v>
       </c>
       <c r="B16" t="n">
-        <v>0.008211150954646961</v>
+        <v>0.0068897024609195</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5712496</v>
+        <v>0.5539849999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.007556233557881233</v>
+        <v>0.007358058482031791</v>
       </c>
       <c r="E16" t="n">
         <v>256</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008289395383720047</v>
+        <v>0.0006901506581791928</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J16" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6582600000000001</v>
+        <v>0.6494199999999999</v>
       </c>
       <c r="B17" t="n">
-        <v>0.005444079352838296</v>
+        <v>0.004867956450092773</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5755668</v>
+        <v>0.5504961500000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006416742084675845</v>
+        <v>0.005557486185880291</v>
       </c>
       <c r="E17" t="n">
         <v>128</v>
       </c>
       <c r="F17" t="n">
-        <v>0.000267775333103133</v>
+        <v>0.0004329677966181864</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -1555,37 +1597,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.65776</v>
+        <v>0.6465000000000001</v>
       </c>
       <c r="B18" t="n">
-        <v>0.004408287649416698</v>
+        <v>0.00346193587462276</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5937209999999999</v>
+        <v>0.55494745</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004572825600080349</v>
+        <v>0.003655003904751694</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0006867090776580455</v>
+        <v>0.0008289395383720047</v>
       </c>
       <c r="G18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.1</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.05</v>
-      </c>
       <c r="I18" t="n">
         <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L18" t="n">
         <v>4</v>
@@ -1593,75 +1635,75 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.65618</v>
+        <v>0.6460399999999999</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003346191865389678</v>
+        <v>0.003176161204976872</v>
       </c>
       <c r="C19" t="n">
-        <v>0.54121025</v>
+        <v>0.5198315</v>
       </c>
       <c r="D19" t="n">
-        <v>0.002948062276733678</v>
+        <v>0.002486340584071304</v>
       </c>
       <c r="E19" t="n">
         <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003284210350911732</v>
+        <v>0.002249198965267357</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J19" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="K19" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.65608</v>
+        <v>0.6459600000000001</v>
       </c>
       <c r="B20" t="n">
-        <v>0.003071970051937368</v>
+        <v>0.005127670036186053</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5750618</v>
+        <v>0.5573995500000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003429470382763221</v>
+        <v>0.004790846569892373</v>
       </c>
       <c r="E20" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0002060924941320236</v>
+        <v>0.0008556226023737445</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J20" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="K20" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
@@ -1669,37 +1711,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.65068</v>
+        <v>0.64408</v>
       </c>
       <c r="B21" t="n">
-        <v>0.004131827682757324</v>
+        <v>0.001961377067266789</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5656667499999999</v>
+        <v>0.5255325</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004418571272906001</v>
+        <v>0.002512298356336285</v>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0008556226023737445</v>
+        <v>0.001793348639944684</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I21" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J21" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="K21" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>

--- a/sepsis_project - Students Version/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/ddqn_ppo_results.xlsx
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.56001744</v>
+        <v>0.562415275</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001585247698468581</v>
+        <v>0.001984994028249816</v>
       </c>
       <c r="D2" t="n">
-        <v>0.65262</v>
+        <v>0.6553599999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001580822570689052</v>
+        <v>0.00215273082386069</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -552,37 +552,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5783678</v>
+        <v>0.5905702249999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001385522064512141</v>
+        <v>0.0008407004027520681</v>
       </c>
       <c r="D3" t="n">
-        <v>0.653272</v>
+        <v>0.66577</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001473268475193836</v>
+        <v>0.0005426785420486039</v>
       </c>
       <c r="F3" t="n">
-        <v>9.385484</v>
+        <v>9.12215</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03496292436281628</v>
+        <v>0.0564843451763408</v>
       </c>
       <c r="H3" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="K3" t="n">
         <v>50000</v>
       </c>
       <c r="L3" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -592,31 +592,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6612539999999999</v>
+        <v>0.6381012750000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002663838947365217</v>
+        <v>0.004203161674003617</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6753279999999999</v>
+        <v>0.67513</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002700614744831261</v>
+        <v>0.004269309077590883</v>
       </c>
       <c r="F4" t="n">
-        <v>7.852116000000001</v>
+        <v>7.898820000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0245460033406661</v>
+        <v>0.03984880173857172</v>
       </c>
       <c r="H4" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,25 +704,45 @@
           <t>gradient_steps</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>train_freq</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>n_step</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>frame_stack</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>is_baseline</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6679</v>
+        <v>0.6684666666666667</v>
       </c>
       <c r="B2" t="n">
-        <v>0.006013734280794266</v>
+        <v>0.00794634786832573</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6079471000000001</v>
+        <v>0.5927955</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006168559451464384</v>
+        <v>0.007709265295012815</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003284210350911732</v>
+        <v>0.0001538065811598203</v>
       </c>
       <c r="G2" t="n">
         <v>0.2</v>
@@ -731,54 +751,28 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J2" t="n">
         <v>50000</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.65678</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.004119101843848972</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.61581535</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.00403991542532144</v>
-      </c>
-      <c r="E3" t="n">
-        <v>256</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.003894923038838411</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I3" t="n">
-        <v>64</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>500</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,57 +852,73 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>frame_stack</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>hidden1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>is_baseline</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6710199999999999</v>
+        <v>0.6803333333333333</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004289172414347559</v>
+        <v>0.007615773105863916</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6403731</v>
+        <v>0.6432121666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004279511598155791</v>
+        <v>0.007730363263169178</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001942663440330811</v>
+        <v>0.0001109309079070013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
         <v>0.3</v>
       </c>
       <c r="H2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>128</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>64</v>
+      </c>
+      <c r="O2" t="n">
+        <v>64</v>
+      </c>
+      <c r="P2" t="b">
         <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1024</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>128</v>
-      </c>
-      <c r="M2" t="n">
-        <v>256</v>
-      </c>
-      <c r="N2" t="n">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,25 +996,40 @@
           <t>gradient_steps</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>train_freq</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>n_step</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>frame_stack</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6679</v>
+        <v>0.6684666666666667</v>
       </c>
       <c r="B2" t="n">
-        <v>0.006013734280794266</v>
+        <v>0.00794634786832573</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6079471000000001</v>
+        <v>0.5927955</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006168559451464384</v>
+        <v>0.007709265295012815</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003284210350911732</v>
+        <v>0.0001538065811598203</v>
       </c>
       <c r="G2" t="n">
         <v>0.2</v>
@@ -1013,124 +1038,151 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J2" t="n">
         <v>50000</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6633199999999999</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002139392437118537</v>
+        <v>0.008180600358300249</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5954849</v>
+        <v>0.5856201666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002012492116444211</v>
+        <v>0.006917090734991888</v>
       </c>
       <c r="E3" t="n">
         <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001073886382247958</v>
+        <v>0.0006918393616565429</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="J3" t="n">
         <v>100000</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.65778</v>
+        <v>0.6637333333333333</v>
       </c>
       <c r="B4" t="n">
-        <v>0.003160221511223521</v>
+        <v>0.006006477984457958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5735627</v>
+        <v>0.5776273333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003127105137943045</v>
+        <v>0.005716029161489613</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001393595487688128</v>
+        <v>0.003560969923212882</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="n">
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.65766</v>
+        <v>0.6637333333333333</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00144499134945508</v>
+        <v>0.006006477984457958</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5602282000000001</v>
+        <v>0.5776273333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001580217265520793</v>
+        <v>0.005716029161489613</v>
       </c>
       <c r="E5" t="n">
         <v>256</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002183935292318299</v>
+        <v>0.003560969923212882</v>
       </c>
       <c r="G5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.1</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.01</v>
-      </c>
       <c r="I5" t="n">
         <v>64</v>
       </c>
       <c r="J5" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="K5" t="n">
         <v>250</v>
@@ -1138,107 +1190,134 @@
       <c r="L5" t="n">
         <v>1</v>
       </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.65706</v>
+        <v>0.6633333333333333</v>
       </c>
       <c r="B6" t="n">
-        <v>0.003698378022863547</v>
+        <v>0.01071343911999214</v>
       </c>
       <c r="C6" t="n">
-        <v>0.59224755</v>
+        <v>0.5874360000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003494640053889656</v>
+        <v>0.009571405627933904</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006867090776580455</v>
+        <v>0.002084982102208431</v>
       </c>
       <c r="G6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.05</v>
-      </c>
       <c r="I6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J6" t="n">
         <v>100000</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.65678</v>
+        <v>0.6615333333333334</v>
       </c>
       <c r="B7" t="n">
-        <v>0.004119101843848972</v>
+        <v>0.007690542532516426</v>
       </c>
       <c r="C7" t="n">
-        <v>0.61581535</v>
+        <v>0.5836936666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00403991542532144</v>
+        <v>0.006908807548058563</v>
       </c>
       <c r="E7" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003894923038838411</v>
+        <v>0.0001538065811598203</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J7" t="n">
         <v>50000</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.65588</v>
+        <v>0.6609333333333333</v>
       </c>
       <c r="B8" t="n">
-        <v>0.005698859535029787</v>
+        <v>0.01178369872135043</v>
       </c>
       <c r="C8" t="n">
-        <v>0.54010475</v>
+        <v>0.5751031666666666</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00602584477220829</v>
+        <v>0.0117443325486759</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0003617355603250917</v>
+        <v>0.0004037506188440757</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I8" t="n">
         <v>64</v>
@@ -1252,101 +1331,128 @@
       <c r="L8" t="n">
         <v>2</v>
       </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.6545400000000001</v>
+        <v>0.6605333333333333</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00240686518110176</v>
+        <v>0.008924373616363496</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5623293</v>
+        <v>0.5724468333333332</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002882284724181499</v>
+        <v>0.008430233854835946</v>
       </c>
       <c r="E9" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008775452610882307</v>
+        <v>0.0006785245383889544</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="J9" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.65438</v>
+        <v>0.6594</v>
       </c>
       <c r="B10" t="n">
-        <v>0.005837550856309508</v>
+        <v>0.01308391718442489</v>
       </c>
       <c r="C10" t="n">
-        <v>0.57569305</v>
+        <v>0.5813064999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006186582741101909</v>
+        <v>0.01274535639022654</v>
       </c>
       <c r="E10" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0002060924941320236</v>
+        <v>0.0006918393616565429</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I10" t="n">
         <v>64</v>
       </c>
       <c r="J10" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="K10" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.65416</v>
+        <v>0.6582666666666667</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001393915348936227</v>
+        <v>0.009041263431868632</v>
       </c>
       <c r="C11" t="n">
-        <v>0.57163995</v>
+        <v>0.5738613333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001670239947208199</v>
+        <v>0.00800078695348154</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001021837675800809</v>
+        <v>0.0001583702374946995</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1355,112 +1461,139 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J11" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="K11" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.65384</v>
+        <v>0.6580666666666666</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004121650154974348</v>
+        <v>0.00628667020148365</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5724329</v>
+        <v>0.5697531666666666</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004052790437618212</v>
+        <v>0.006163064753252031</v>
       </c>
       <c r="E12" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0003793280795162164</v>
+        <v>0.0008452526848156869</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J12" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
       </c>
       <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6531</v>
+        <v>0.6570666666666666</v>
       </c>
       <c r="B13" t="n">
-        <v>0.004848195540610958</v>
+        <v>0.003600925806881734</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5520993</v>
+        <v>0.5642419999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00547510961191646</v>
+        <v>0.003677742863421078</v>
       </c>
       <c r="E13" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001040166367988732</v>
+        <v>0.0006785245383889544</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H13" t="n">
         <v>0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="J13" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K13" t="n">
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.65266</v>
+        <v>0.6564</v>
       </c>
       <c r="B14" t="n">
-        <v>0.008595231235981963</v>
+        <v>0.01231394873033559</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5775380999999999</v>
+        <v>0.5667131666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008555990380648554</v>
+        <v>0.0120766980977602</v>
       </c>
       <c r="E14" t="n">
         <v>128</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001423638128723575</v>
+        <v>0.0002404511340335502</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1472,7 +1605,7 @@
         <v>64</v>
       </c>
       <c r="J14" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K14" t="n">
         <v>100</v>
@@ -1480,177 +1613,222 @@
       <c r="L14" t="n">
         <v>2</v>
       </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6502800000000001</v>
+        <v>0.6561999999999999</v>
       </c>
       <c r="B15" t="n">
-        <v>0.005965064961926255</v>
+        <v>0.01470185173522179</v>
       </c>
       <c r="C15" t="n">
-        <v>0.55648105</v>
+        <v>0.5754233333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>0.005811125031996836</v>
+        <v>0.01579686863528833</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000267775333103133</v>
+        <v>0.00309437714708314</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="J15" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6501400000000001</v>
+        <v>0.6555333333333333</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0068897024609195</v>
+        <v>0.008902558933001001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5539849999999999</v>
+        <v>0.5697481666666666</v>
       </c>
       <c r="D16" t="n">
-        <v>0.007358058482031791</v>
+        <v>0.008163999083884431</v>
       </c>
       <c r="E16" t="n">
         <v>256</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0006901506581791928</v>
+        <v>0.0008986552644007198</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="n">
         <v>128</v>
       </c>
       <c r="J16" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="K16" t="n">
         <v>250</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6494199999999999</v>
+        <v>0.6554</v>
       </c>
       <c r="B17" t="n">
-        <v>0.004867956450092773</v>
+        <v>0.007628164188642597</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5504961500000001</v>
+        <v>0.5690043333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.005557486185880291</v>
+        <v>0.008538475875575101</v>
       </c>
       <c r="E17" t="n">
         <v>128</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0004329677966181864</v>
+        <v>0.001040166367988732</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="n">
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="J17" t="n">
         <v>10000</v>
       </c>
       <c r="K17" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
       </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.6465000000000001</v>
+        <v>0.6545333333333333</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00346193587462276</v>
+        <v>0.003387886919272498</v>
       </c>
       <c r="C18" t="n">
-        <v>0.55494745</v>
+        <v>0.5686686666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003655003904751694</v>
+        <v>0.002754448081941467</v>
       </c>
       <c r="E18" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0008289395383720047</v>
+        <v>0.001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I18" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J18" t="n">
         <v>50000</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.6460399999999999</v>
+        <v>0.6544666666666668</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003176161204976872</v>
+        <v>0.008295246295988492</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5198315</v>
+        <v>0.5692238333333334</v>
       </c>
       <c r="D19" t="n">
-        <v>0.002486340584071304</v>
+        <v>0.008818928104745286</v>
       </c>
       <c r="E19" t="n">
         <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>0.002249198965267357</v>
+        <v>0.004093813608598782</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1659,36 +1837,45 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J19" t="n">
         <v>10000</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6459600000000001</v>
+        <v>0.6543333333333333</v>
       </c>
       <c r="B20" t="n">
-        <v>0.005127670036186053</v>
+        <v>0.006603870918719658</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5573995500000001</v>
+        <v>0.5654633333333334</v>
       </c>
       <c r="D20" t="n">
-        <v>0.004790846569892373</v>
+        <v>0.007216974950112811</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0008556226023737445</v>
+        <v>0.0001538065811598203</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1697,36 +1884,45 @@
         <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J20" t="n">
         <v>10000</v>
       </c>
       <c r="K20" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.64408</v>
+        <v>0.6541333333333332</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001961377067266789</v>
+        <v>0.003663635110409119</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5255325</v>
+        <v>0.565453</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002512298356336285</v>
+        <v>0.003853264245704187</v>
       </c>
       <c r="E21" t="n">
         <v>256</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001793348639944684</v>
+        <v>0.003560969923212882</v>
       </c>
       <c r="G21" t="n">
         <v>0.1</v>
@@ -1744,6 +1940,485 @@
         <v>250</v>
       </c>
       <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.6527999999999999</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.009051089559949252</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5585016666666667</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.007620752027085884</v>
+      </c>
+      <c r="E22" t="n">
+        <v>128</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0008452526848156869</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" t="n">
+        <v>64</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>100</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.6527333333333333</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.008297924774035693</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5625968333333333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.009431187410513162</v>
+      </c>
+      <c r="E23" t="n">
+        <v>64</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.001040166367988732</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>256</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.6501333333333333</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.008918146294681049</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.5542008333333333</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.008532682531335373</v>
+      </c>
+      <c r="E24" t="n">
+        <v>256</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.004093813608598782</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I24" t="n">
+        <v>128</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.6501333333333333</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0115147248724791</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5532908333333333</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.01096997828672018</v>
+      </c>
+      <c r="E25" t="n">
+        <v>128</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0001574722143617989</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I25" t="n">
+        <v>64</v>
+      </c>
+      <c r="J25" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>100</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.6497333333333334</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.01463898903613225</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5657586666666666</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.01583138894420758</v>
+      </c>
+      <c r="E26" t="n">
+        <v>256</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.001210526448041934</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I26" t="n">
+        <v>64</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>100</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.6470666666666667</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.00952598784612097</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5494861666666667</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.01042243084849529</v>
+      </c>
+      <c r="E27" t="n">
+        <v>128</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0004254891877710625</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I27" t="n">
+        <v>64</v>
+      </c>
+      <c r="J27" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.6466666666666667</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.01218605760695393</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5612531666666667</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.01066268140721021</v>
+      </c>
+      <c r="E28" t="n">
+        <v>64</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.002084982102208431</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>128</v>
+      </c>
+      <c r="J28" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>500</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.6466666666666667</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.01218605760695393</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5612531666666667</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01066268140721021</v>
+      </c>
+      <c r="E29" t="n">
+        <v>64</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.002084982102208431</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>128</v>
+      </c>
+      <c r="J29" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>500</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0.6464</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.006378784279852144</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5569788333333333</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.00663253472474892</v>
+      </c>
+      <c r="E30" t="n">
+        <v>128</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0004254891877710625</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I30" t="n">
+        <v>256</v>
+      </c>
+      <c r="J30" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0.6445333333333334</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.002180723631172792</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5548176666666667</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.001056981649951121</v>
+      </c>
+      <c r="E31" t="n">
+        <v>256</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0001574722143617989</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I31" t="n">
+        <v>64</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>250</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1758,7 +2433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,10 +2499,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>frame_stack</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>hidden1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
         </is>
@@ -1835,34 +2515,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6710199999999999</v>
+        <v>0.6803333333333333</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004289172414347559</v>
+        <v>0.007615773105863916</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6403731</v>
+        <v>0.6432121666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004279511598155791</v>
+        <v>0.007730363263169178</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001942663440330811</v>
+        <v>0.0001109309079070013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
         <v>0.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -1871,39 +2551,42 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
+        <v>64</v>
+      </c>
+      <c r="O2" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6704399999999999</v>
+        <v>0.673</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004519181341791912</v>
+        <v>0.009371943946339716</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6117704500000001</v>
+        <v>0.6266681666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004731487128799963</v>
+        <v>0.008575574029215523</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001090049253729382</v>
+        <v>0.0001082369313330419</v>
       </c>
       <c r="F3" t="n">
         <v>0.9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>512</v>
@@ -1912,45 +2595,48 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
+        <v>64</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O3" t="n">
         <v>256</v>
-      </c>
-      <c r="M3" t="n">
-        <v>128</v>
-      </c>
-      <c r="N3" t="n">
-        <v>128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.67034</v>
+        <v>0.6704666666666667</v>
       </c>
       <c r="B4" t="n">
-        <v>0.003693643187964954</v>
+        <v>0.009106163968555698</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6305271</v>
+        <v>0.6179198333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003490899336131028</v>
+        <v>0.008702535099198267</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002139331892500008</v>
+        <v>0.0002342281583504994</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -1959,33 +2645,36 @@
         <v>64</v>
       </c>
       <c r="M4" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>64</v>
+        <v>128</v>
+      </c>
+      <c r="O4" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.66784</v>
+        <v>0.6702666666666667</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003360505914293274</v>
+        <v>0.00827445869327215</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6135873500000001</v>
+        <v>0.5882746666666666</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003734496027745891</v>
+        <v>0.00711096970454023</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0005016631968599064</v>
+        <v>0.002124581964224018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="n">
         <v>0.01</v>
@@ -1994,89 +2683,95 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>64</v>
       </c>
       <c r="M5" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>64</v>
+      </c>
+      <c r="O5" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.66554</v>
+        <v>0.6695333333333334</v>
       </c>
       <c r="B6" t="n">
-        <v>0.005697631086688569</v>
+        <v>0.01009840471449713</v>
       </c>
       <c r="C6" t="n">
-        <v>0.603576</v>
+        <v>0.624738</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00579754870343926</v>
+        <v>0.009930559956098447</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003574712922600246</v>
+        <v>0.0003757492064184008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>512</v>
+        <v>2048</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="M6" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>256</v>
       </c>
+      <c r="O6" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.6654</v>
+        <v>0.6682</v>
       </c>
       <c r="B7" t="n">
-        <v>0.005250238089839329</v>
+        <v>0.006044281043543029</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5916872999999999</v>
+        <v>0.633446</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005816727917717116</v>
+        <v>0.006169722593034497</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002710864828729778</v>
+        <v>0.0001109309079070013</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
         <v>0.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -2085,39 +2780,42 @@
         <v>512</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="M7" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>256</v>
+        <v>64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.6643600000000001</v>
+        <v>0.6675333333333333</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008816632010013781</v>
+        <v>0.004598308867882274</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5983796000000001</v>
+        <v>0.5953491666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008579123302747769</v>
+        <v>0.005142094221823548</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002322119672134761</v>
+        <v>0.000117115099555241</v>
       </c>
       <c r="F8" t="n">
         <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="n">
         <v>0.05</v>
@@ -2129,77 +2827,83 @@
         <v>2048</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="M8" t="n">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>256</v>
+        <v>64</v>
+      </c>
+      <c r="O8" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.66106</v>
+        <v>0.6646666666666667</v>
       </c>
       <c r="B9" t="n">
-        <v>0.006753739704785792</v>
+        <v>0.007039570693980959</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6009727500000002</v>
+        <v>0.5720886666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006823586655399806</v>
+        <v>0.005826910916886673</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003571439909823144</v>
+        <v>0.0003</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="n">
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>1024</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>256</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>256</v>
+        <v>128</v>
+      </c>
+      <c r="O9" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.6607200000000001</v>
+        <v>0.6644</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00224988888614525</v>
+        <v>0.004335896677735775</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5797524000000001</v>
+        <v>0.5836666666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001808292017001139</v>
+        <v>0.006303175318616966</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0004135867955263891</v>
+        <v>0.002900210932479527</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -2211,51 +2915,54 @@
         <v>0.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>512</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="M10" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>128</v>
+        <v>64</v>
+      </c>
+      <c r="O10" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.66042</v>
+        <v>0.6644</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001460136979875521</v>
+        <v>0.004335896677735775</v>
       </c>
       <c r="C11" t="n">
-        <v>0.589828</v>
+        <v>0.5836666666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00253930730589076</v>
+        <v>0.006303175318616966</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001972161097057403</v>
+        <v>0.002900210932479527</v>
       </c>
       <c r="F11" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>512</v>
@@ -2264,74 +2971,80 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>64</v>
+      </c>
+      <c r="O11" t="n">
         <v>256</v>
-      </c>
-      <c r="N11" t="n">
-        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.65938</v>
+        <v>0.6639333333333334</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00595961408146534</v>
+        <v>0.01133921416050418</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5977151000000001</v>
+        <v>0.6254233333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006062735432542</v>
+        <v>0.01128825989505618</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0008099164993582627</v>
+        <v>0.0002342281583504994</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
+        <v>128</v>
+      </c>
+      <c r="O12" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.65864</v>
+        <v>0.6636000000000001</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003908068576675706</v>
+        <v>0.008920637745014517</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5731065999999999</v>
+        <v>0.5950810000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003664884085820468</v>
+        <v>0.01001351977398003</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0009836162684900027</v>
+        <v>0.0001082369313330419</v>
       </c>
       <c r="F13" t="n">
         <v>0.9</v>
@@ -2340,13 +3053,13 @@
         <v>0.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
@@ -2355,33 +3068,36 @@
         <v>128</v>
       </c>
       <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>128</v>
+      </c>
+      <c r="O13" t="n">
         <v>256</v>
-      </c>
-      <c r="N13" t="n">
-        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.6582999999999999</v>
+        <v>0.6631333333333334</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002469817807045685</v>
+        <v>0.01214633003558415</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5925770499999999</v>
+        <v>0.6085526666666666</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002450955779129859</v>
+        <v>0.01201604825905299</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001017364485544502</v>
+        <v>0.0001133669581784054</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H14" t="n">
         <v>0.05</v>
@@ -2399,83 +3115,89 @@
         <v>128</v>
       </c>
       <c r="M14" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>128</v>
+        <v>64</v>
+      </c>
+      <c r="O14" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.65816</v>
+        <v>0.6626666666666667</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00359485743806343</v>
+        <v>0.009935905707192601</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5887751</v>
+        <v>0.6141163333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004061269642919573</v>
+        <v>0.00964585530235074</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0003384522041201141</v>
+        <v>0.0003574712922600246</v>
       </c>
       <c r="F15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
         <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="K15" t="n">
         <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>64</v>
+        <v>256</v>
+      </c>
+      <c r="O15" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6575399999999999</v>
+        <v>0.6622</v>
       </c>
       <c r="B16" t="n">
-        <v>0.006503306851133519</v>
+        <v>0.004891034882539889</v>
       </c>
       <c r="C16" t="n">
-        <v>0.56382235</v>
+        <v>0.5890845</v>
       </c>
       <c r="D16" t="n">
-        <v>0.006760492788066577</v>
+        <v>0.005018465921806476</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002190714227215282</v>
+        <v>0.000874479618932312</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>2048</v>
@@ -2487,27 +3209,30 @@
         <v>64</v>
       </c>
       <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
         <v>256</v>
       </c>
-      <c r="N16" t="n">
-        <v>64</v>
+      <c r="O16" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.65586</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="B17" t="n">
-        <v>0.002910841802640583</v>
+        <v>0.006176118881987661</v>
       </c>
       <c r="C17" t="n">
-        <v>0.58271035</v>
+        <v>0.573807</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003388411056454054</v>
+        <v>0.00449175790723655</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0004841041099321571</v>
+        <v>0.0003757492064184008</v>
       </c>
       <c r="F17" t="n">
         <v>0.95</v>
@@ -2516,10 +3241,10 @@
         <v>0.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>2048</v>
@@ -2528,77 +3253,83 @@
         <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
         <v>256</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.6548</v>
+        <v>0.6616666666666666</v>
       </c>
       <c r="B18" t="n">
-        <v>0.002434132288927602</v>
+        <v>0.008806563209081967</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5642702000000001</v>
+        <v>0.58033</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002061406470713636</v>
+        <v>0.009765279196099692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0004872420129560896</v>
+        <v>0.000117115099555241</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I18" t="n">
         <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>512</v>
+        <v>2048</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="M18" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>64</v>
+      </c>
+      <c r="O18" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.65364</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="B19" t="n">
-        <v>0.002374447304111025</v>
+        <v>0.008351979140033534</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5672216000000001</v>
+        <v>0.5491064999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0027174213742075</v>
+        <v>0.0067540817751194</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002904665979638735</v>
+        <v>0.001538583627271403</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G19" t="n">
         <v>0.2</v>
@@ -2619,98 +3350,577 @@
         <v>128</v>
       </c>
       <c r="M19" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>128</v>
+        <v>64</v>
+      </c>
+      <c r="O19" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.65108</v>
+        <v>0.6593333333333333</v>
       </c>
       <c r="B20" t="n">
-        <v>0.003535109616405126</v>
+        <v>0.008618455649231922</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5578465499999999</v>
+        <v>0.6154338333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003750391768702331</v>
+        <v>0.008772310101329591</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002442046084491142</v>
+        <v>0.0001109309079070013</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H20" t="n">
         <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="M20" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>128</v>
+        <v>64</v>
+      </c>
+      <c r="O20" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.65038</v>
+        <v>0.6592666666666667</v>
       </c>
       <c r="B21" t="n">
-        <v>0.004649408564538066</v>
+        <v>0.007882470002057326</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5759699</v>
+        <v>0.5784483333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004243689707229974</v>
+        <v>0.007819880424988049</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002458429052828939</v>
+        <v>0.00129667438075127</v>
       </c>
       <c r="F21" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="M21" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>256</v>
+      </c>
+      <c r="O21" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.6591333333333333</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.009263428690885004</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5703053333333334</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.00877748537531608</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0007114706514580523</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>64</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>128</v>
+      </c>
+      <c r="O22" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.6587333333333334</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.006197669813011292</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6148416666666667</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.005131588312707029</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0008974255743856962</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>512</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>128</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>64</v>
+      </c>
+      <c r="O23" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.6574000000000001</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.006043361831151793</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6001983333333334</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.006146507222941039</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0001082369313330419</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>512</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" t="n">
+        <v>128</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>128</v>
+      </c>
+      <c r="O24" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.6568666666666667</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.007274766128352315</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6066775</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.007711554214474369</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.000116628902739314</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>512</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>128</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>64</v>
+      </c>
+      <c r="O25" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.6562666666666667</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.004974378799854757</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5849096666666667</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.004568320245025632</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0003575594457014808</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" t="n">
+        <v>128</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>256</v>
+      </c>
+      <c r="O26" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.6559333333333334</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.008961026726887948</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5798715000000001</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.01031180587562947</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0001082369313330419</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" t="n">
+        <v>128</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>128</v>
+      </c>
+      <c r="O27" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.6527999999999999</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.00856219078922627</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5459661666666668</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.008816770175038256</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000874479618932312</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>512</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>64</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>256</v>
+      </c>
+      <c r="O28" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.6516666666666666</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.002121320343559636</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5808126666666666</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.001536305927469466</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0003575594457014808</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>512</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>64</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>128</v>
+      </c>
+      <c r="O29" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0.6504000000000001</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.004889898885571238</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.56786</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.005088590655683666</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.000874479618932312</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>64</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>128</v>
+      </c>
+      <c r="O30" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0.6476</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.008948618763685143</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5742735</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.008613421140870825</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0001133669581784054</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>512</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>64</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>256</v>
+      </c>
+      <c r="O31" t="n">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2754,13 +3964,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6604549999999999</v>
+        <v>0.67908</v>
       </c>
       <c r="C2" t="n">
-        <v>0.674</v>
+        <v>0.714</v>
       </c>
       <c r="D2" t="n">
-        <v>7.65</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3">
@@ -2768,13 +3978,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.69631</v>
+        <v>0.7124200000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.71</v>
+        <v>0.752</v>
       </c>
       <c r="D3" t="n">
-        <v>7.884</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="4">
@@ -2782,13 +3992,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.67675</v>
+        <v>0.6599700000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="D4" t="n">
-        <v>8.173999999999999</v>
+        <v>8.077999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2796,13 +4006,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6855450000000001</v>
+        <v>0.6872500000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.698</v>
+        <v>0.724</v>
       </c>
       <c r="D5" t="n">
-        <v>7.632</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="6">
@@ -2810,13 +4020,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.67395</v>
+        <v>0.62602</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="D6" t="n">
-        <v>7.734</v>
+        <v>7.426</v>
       </c>
     </row>
   </sheetData>
@@ -2860,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.677465</v>
+        <v>0.644815</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>8.06</v>
+        <v>8.144</v>
       </c>
     </row>
     <row r="3">
@@ -2874,13 +4084,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6490050000000001</v>
+        <v>0.642595</v>
       </c>
       <c r="C3" t="n">
-        <v>0.664</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>7.954</v>
+        <v>8.304</v>
       </c>
     </row>
     <row r="4">
@@ -2888,13 +4098,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.67675</v>
+        <v>0.6599700000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="D4" t="n">
-        <v>8.173999999999999</v>
+        <v>8.077999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2902,13 +4112,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6402</v>
+        <v>0.669585</v>
       </c>
       <c r="C5" t="n">
-        <v>0.654</v>
+        <v>0.708</v>
       </c>
       <c r="D5" t="n">
-        <v>7.688</v>
+        <v>8.273999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2916,13 +4126,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6636599999999999</v>
+        <v>0.66203</v>
       </c>
       <c r="C6" t="n">
-        <v>0.678</v>
+        <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>8.01</v>
+        <v>8.256</v>
       </c>
     </row>
   </sheetData>
@@ -2966,13 +4176,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.701065</v>
+        <v>0.6820350000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.716</v>
+        <v>0.724</v>
       </c>
       <c r="D2" t="n">
-        <v>8.554</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2980,13 +4190,13 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6368199999999999</v>
+        <v>0.6546150000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.65</v>
+        <v>0.694</v>
       </c>
       <c r="D3" t="n">
-        <v>7.536</v>
+        <v>8.036</v>
       </c>
     </row>
     <row r="4">
@@ -2994,13 +4204,13 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.67675</v>
+        <v>0.6599700000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="D4" t="n">
-        <v>8.173999999999999</v>
+        <v>8.077999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3008,13 +4218,13 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5903400000000001</v>
+        <v>0.5724900000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.604</v>
+        <v>0.606</v>
       </c>
       <c r="D5" t="n">
-        <v>7.282</v>
+        <v>7.246</v>
       </c>
     </row>
     <row r="6">
@@ -3022,13 +4232,13 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5021100000000001</v>
+        <v>0.47761</v>
       </c>
       <c r="C6" t="n">
-        <v>0.512</v>
+        <v>0.506</v>
       </c>
       <c r="D6" t="n">
-        <v>5.842</v>
+        <v>5.91</v>
       </c>
     </row>
   </sheetData>

--- a/sepsis_project - Students Version/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/ddqn_ppo_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,27 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Best Trial</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Best Checkpoint Episode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Checkpoint Survival</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Checkpoint Return</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>buffer_size</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>target_update_freq</t>
         </is>
       </c>
     </row>
@@ -504,16 +519,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.562415275</v>
+        <v>0.56438975</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001984994028249816</v>
+        <v>0.00189883667511186</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6553599999999999</v>
+        <v>0.6569199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00215273082386069</v>
+        <v>0.002203576638104502</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,6 +559,21 @@
           <t>-</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -552,22 +582,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5905702249999999</v>
+        <v>0.6149963749999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008407004027520681</v>
+        <v>0.004336154644562683</v>
       </c>
       <c r="D3" t="n">
-        <v>0.66577</v>
+        <v>0.6648000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005426785420486039</v>
+        <v>0.004428741356186892</v>
       </c>
       <c r="F3" t="n">
-        <v>9.12215</v>
+        <v>7.93232</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0564843451763408</v>
+        <v>0.04284701856605676</v>
       </c>
       <c r="H3" t="n">
         <v>20000</v>
@@ -579,10 +609,19 @@
         <v>20000</v>
       </c>
       <c r="K3" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>250</v>
+        <v>14000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6624000000000001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6134309999999999</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="4">
@@ -592,22 +631,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6381012750000001</v>
+        <v>0.6570703</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004203161674003617</v>
+        <v>0.004027793431466224</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67513</v>
+        <v>0.68104</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004269309077590883</v>
+        <v>0.003998499718644489</v>
       </c>
       <c r="F4" t="n">
-        <v>7.898820000000001</v>
+        <v>7.35084</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03984880173857172</v>
+        <v>0.04251423879125683</v>
       </c>
       <c r="H4" t="n">
         <v>20000</v>
@@ -618,12 +657,19 @@
       <c r="J4" t="n">
         <v>20000</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A (on-policy)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="n">
+        <v>18000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6916</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6679980000000001</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>N/A (on-policy)</t>
         </is>
@@ -640,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,56 +742,31 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>target_update_freq</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>gradient_steps</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>train_freq</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>n_step</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>frame_stack</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>is_baseline</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6684666666666667</v>
+        <v>0.6648000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00794634786832573</v>
+        <v>0.004428741356186892</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5927955</v>
+        <v>0.6149963749999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007709265295012815</v>
+        <v>0.004336154644562683</v>
       </c>
       <c r="E2" t="n">
         <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001538065811598203</v>
+        <v>0.001040166367988732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
         <v>0.01</v>
@@ -754,25 +775,10 @@
         <v>64</v>
       </c>
       <c r="J2" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,73 +858,57 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>frame_stack</t>
+          <t>hidden1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>hidden1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>hidden2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>is_baseline</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6803333333333333</v>
+        <v>0.68104</v>
       </c>
       <c r="B2" t="n">
-        <v>0.007615773105863916</v>
+        <v>0.003998499718644489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6432121666666667</v>
+        <v>0.6570703</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007730363263169178</v>
+        <v>0.004027793431466224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001109309079070013</v>
+        <v>0.0001090049253729382</v>
       </c>
       <c r="F2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="N2" t="n">
-        <v>64</v>
-      </c>
-      <c r="O2" t="n">
-        <v>64</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,51 +978,31 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>target_update_freq</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>gradient_steps</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>train_freq</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>n_step</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>frame_stack</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6684666666666667</v>
+        <v>0.6648000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00794634786832573</v>
+        <v>0.004428741356186892</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5927955</v>
+        <v>0.6149963749999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007709265295012815</v>
+        <v>0.004336154644562683</v>
       </c>
       <c r="E2" t="n">
         <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001538065811598203</v>
+        <v>0.001040166367988732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
         <v>0.01</v>
@@ -1041,277 +1011,205 @@
         <v>64</v>
       </c>
       <c r="J2" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6645800000000001</v>
       </c>
       <c r="B3" t="n">
-        <v>0.008180600358300249</v>
+        <v>0.003255495354012994</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5856201666666667</v>
+        <v>0.6134201000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006917090734991888</v>
+        <v>0.003635447710779564</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006918393616565429</v>
+        <v>0.001190201204959624</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K3" t="n">
-        <v>250</v>
-      </c>
-      <c r="L3" t="n">
         <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6637333333333333</v>
+        <v>0.65984</v>
       </c>
       <c r="B4" t="n">
-        <v>0.006006477984457958</v>
+        <v>0.004104174703883874</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5776273333333333</v>
+        <v>0.560249475</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005716029161489613</v>
+        <v>0.004116016941663689</v>
       </c>
       <c r="E4" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003560969923212882</v>
+        <v>0.00397667839903973</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J4" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="K4" t="n">
-        <v>250</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.6637333333333333</v>
+        <v>0.6593600000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>0.006006477984457958</v>
+        <v>0.004635380243302586</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5776273333333333</v>
+        <v>0.5688668750000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005716029161489613</v>
+        <v>0.004179748606562636</v>
       </c>
       <c r="E5" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003560969923212882</v>
+        <v>0.000714439313109744</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J5" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="K5" t="n">
-        <v>250</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.6577999999999999</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01071343911999214</v>
+        <v>0.004344968354315121</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5874360000000001</v>
+        <v>0.558401275</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009571405627933904</v>
+        <v>0.004169584052059305</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002084982102208431</v>
+        <v>0.0004574578205475404</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I6" t="n">
         <v>128</v>
       </c>
       <c r="J6" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.6615333333333334</v>
+        <v>0.65759</v>
       </c>
       <c r="B7" t="n">
-        <v>0.007690542532516426</v>
+        <v>0.004451179618932517</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5836936666666667</v>
+        <v>0.54107985</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006908807548058563</v>
+        <v>0.004275967256620135</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001538065811598203</v>
+        <v>0.001281334807364802</v>
       </c>
       <c r="G7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.01</v>
-      </c>
       <c r="I7" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J7" t="n">
         <v>50000</v>
       </c>
       <c r="K7" t="n">
-        <v>250</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.6609333333333333</v>
+        <v>0.6572800000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01178369872135043</v>
+        <v>0.001830505394692945</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5751031666666666</v>
+        <v>0.57401685</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0117443325486759</v>
+        <v>0.001733797508361386</v>
       </c>
       <c r="E8" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0004037506188440757</v>
+        <v>0.000316417019548443</v>
       </c>
       <c r="G8" t="n">
         <v>0.1</v>
@@ -1320,474 +1218,354 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J8" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.6605333333333333</v>
+        <v>0.65725</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008924373616363496</v>
+        <v>0.001432654878189446</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5724468333333332</v>
+        <v>0.575302975</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008430233854835946</v>
+        <v>0.001710698693151393</v>
       </c>
       <c r="E9" t="n">
+        <v>128</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0003135775732257748</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" t="n">
         <v>64</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0006785245383889544</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I9" t="n">
-        <v>256</v>
       </c>
       <c r="J9" t="n">
         <v>100000</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.6594</v>
+        <v>0.65712</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01308391718442489</v>
+        <v>0.002935685609870385</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5813064999999999</v>
+        <v>0.55711575</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01274535639022654</v>
+        <v>0.003401699950713934</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0006918393616565429</v>
+        <v>0.0007610438922351127</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="n">
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J10" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K10" t="n">
-        <v>250</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.6582666666666667</v>
+        <v>0.6561600000000001</v>
       </c>
       <c r="B11" t="n">
-        <v>0.009041263431868632</v>
+        <v>0.001404635183953495</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5738613333333333</v>
+        <v>0.52013205</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00800078695348154</v>
+        <v>0.0007560516609746166</v>
       </c>
       <c r="E11" t="n">
         <v>128</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001583702374946995</v>
+        <v>0.0003153579159668694</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="n">
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J11" t="n">
         <v>50000</v>
       </c>
       <c r="K11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
         <v>4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.6580666666666666</v>
+        <v>0.6551100000000001</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00628667020148365</v>
+        <v>0.002957913115694912</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5697531666666666</v>
+        <v>0.552511875</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006163064753252031</v>
+        <v>0.002632115987245345</v>
       </c>
       <c r="E12" t="n">
         <v>128</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0008452526848156869</v>
+        <v>0.0002074803317589487</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H12" t="n">
         <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J12" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
-      </c>
-      <c r="L12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6570666666666666</v>
+        <v>0.65505</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003600925806881734</v>
+        <v>0.006248499819956788</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5642419999999999</v>
+        <v>0.5322492999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003677742863421078</v>
+        <v>0.005666194542939547</v>
       </c>
       <c r="E13" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006785245383889544</v>
+        <v>0.0008746431657116674</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I13" t="n">
-        <v>256</v>
+        <v>32</v>
       </c>
       <c r="J13" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.6564</v>
+        <v>0.6545300000000001</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01231394873033559</v>
+        <v>0.006243356469079743</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5667131666666667</v>
+        <v>0.5517352250000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0120766980977602</v>
+        <v>0.005832954921178442</v>
       </c>
       <c r="E14" t="n">
         <v>128</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002404511340335502</v>
+        <v>0.00124775471175797</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I14" t="n">
         <v>64</v>
       </c>
       <c r="J14" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6561999999999999</v>
+        <v>0.6538700000000001</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01470185173522179</v>
+        <v>0.003141576037596425</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5754233333333333</v>
+        <v>0.5442390500000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01579686863528833</v>
+        <v>0.002914186320559754</v>
       </c>
       <c r="E15" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00309437714708314</v>
+        <v>0.000353747484467483</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>256</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K15" t="n">
-        <v>250</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6555333333333333</v>
+        <v>0.65374</v>
       </c>
       <c r="B16" t="n">
-        <v>0.008902558933001001</v>
+        <v>0.001945957347939582</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5697481666666666</v>
+        <v>0.5501119750000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.008163999083884431</v>
+        <v>0.001278760946311857</v>
       </c>
       <c r="E16" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008986552644007198</v>
+        <v>0.0001104552426030473</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I16" t="n">
         <v>128</v>
       </c>
       <c r="J16" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="K16" t="n">
-        <v>250</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6554</v>
+        <v>0.65364</v>
       </c>
       <c r="B17" t="n">
-        <v>0.007628164188642597</v>
+        <v>0.003791503659499751</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5690043333333333</v>
+        <v>0.5561039250000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.008538475875575101</v>
+        <v>0.003377297938302532</v>
       </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001040166367988732</v>
+        <v>0.0002577772852685678</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H17" t="n">
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
         <v>10000</v>
       </c>
       <c r="K17" t="n">
-        <v>250</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.6545333333333333</v>
+        <v>0.65341</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003387886919272498</v>
+        <v>0.003222072314520558</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5686686666666667</v>
+        <v>0.5989162</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002754448081941467</v>
+        <v>0.003187032069329921</v>
       </c>
       <c r="E18" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>0.001</v>
+        <v>0.00069389014127394</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I18" t="n">
         <v>128</v>
@@ -1796,86 +1574,62 @@
         <v>50000</v>
       </c>
       <c r="K18" t="n">
-        <v>250</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.6544666666666668</v>
+        <v>0.6527399999999999</v>
       </c>
       <c r="B19" t="n">
-        <v>0.008295246295988492</v>
+        <v>0.002235900266112059</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5692238333333334</v>
+        <v>0.548358225</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008818928104745286</v>
+        <v>0.001796039987288008</v>
       </c>
       <c r="E19" t="n">
         <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>0.004093813608598782</v>
+        <v>0.0001573468512939367</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I19" t="n">
         <v>128</v>
       </c>
       <c r="J19" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K19" t="n">
-        <v>500</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3</v>
-      </c>
-      <c r="O19" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6543333333333333</v>
+        <v>0.6518699999999999</v>
       </c>
       <c r="B20" t="n">
-        <v>0.006603870918719658</v>
+        <v>0.003700439163126457</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5654633333333334</v>
+        <v>0.56084225</v>
       </c>
       <c r="D20" t="n">
-        <v>0.007216974950112811</v>
+        <v>0.003368400435249298</v>
       </c>
       <c r="E20" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001538065811598203</v>
+        <v>0.0003067785513876972</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1890,536 +1644,42 @@
         <v>10000</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.6541333333333332</v>
+        <v>0.65051</v>
       </c>
       <c r="B21" t="n">
-        <v>0.003663635110409119</v>
+        <v>0.002152150087702971</v>
       </c>
       <c r="C21" t="n">
-        <v>0.565453</v>
+        <v>0.5566139</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003853264245704187</v>
+        <v>0.002556643671398082</v>
       </c>
       <c r="E21" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003560969923212882</v>
+        <v>0.001112527727653784</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H21" t="n">
         <v>0.1</v>
       </c>
       <c r="I21" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="K21" t="n">
-        <v>250</v>
-      </c>
-      <c r="L21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.6527999999999999</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.009051089559949252</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.5585016666666667</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.007620752027085884</v>
-      </c>
-      <c r="E22" t="n">
-        <v>128</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.0008452526848156869</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I22" t="n">
-        <v>64</v>
-      </c>
-      <c r="J22" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0.6527333333333333</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.008297924774035693</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.5625968333333333</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.009431187410513162</v>
-      </c>
-      <c r="E23" t="n">
-        <v>64</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.001040166367988732</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I23" t="n">
-        <v>256</v>
-      </c>
-      <c r="J23" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.6501333333333333</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.008918146294681049</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.5542008333333333</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.008532682531335373</v>
-      </c>
-      <c r="E24" t="n">
-        <v>256</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.004093813608598782</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I24" t="n">
-        <v>128</v>
-      </c>
-      <c r="J24" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>100</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0.6501333333333333</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.0115147248724791</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.5532908333333333</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.01096997828672018</v>
-      </c>
-      <c r="E25" t="n">
-        <v>128</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.0001574722143617989</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I25" t="n">
-        <v>64</v>
-      </c>
-      <c r="J25" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K25" t="n">
-        <v>100</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0.6497333333333334</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.01463898903613225</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.5657586666666666</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.01583138894420758</v>
-      </c>
-      <c r="E26" t="n">
-        <v>256</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.001210526448041934</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I26" t="n">
-        <v>64</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0.6470666666666667</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.00952598784612097</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.5494861666666667</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.01042243084849529</v>
-      </c>
-      <c r="E27" t="n">
-        <v>128</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0004254891877710625</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I27" t="n">
-        <v>64</v>
-      </c>
-      <c r="J27" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>100</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0.6466666666666667</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.01218605760695393</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5612531666666667</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.01066268140721021</v>
-      </c>
-      <c r="E28" t="n">
-        <v>64</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.002084982102208431</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>128</v>
-      </c>
-      <c r="J28" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>500</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0.6466666666666667</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.01218605760695393</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.5612531666666667</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.01066268140721021</v>
-      </c>
-      <c r="E29" t="n">
-        <v>64</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.002084982102208431</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>128</v>
-      </c>
-      <c r="J29" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>500</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>0.6464</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.006378784279852144</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.5569788333333333</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.00663253472474892</v>
-      </c>
-      <c r="E30" t="n">
-        <v>128</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0004254891877710625</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I30" t="n">
-        <v>256</v>
-      </c>
-      <c r="J30" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>100</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>0.6445333333333334</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.002180723631172792</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.5548176666666667</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.001056981649951121</v>
-      </c>
-      <c r="E31" t="n">
-        <v>256</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0001574722143617989</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I31" t="n">
-        <v>64</v>
-      </c>
-      <c r="J31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K31" t="n">
-        <v>250</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2433,7 +1693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2499,15 +1759,10 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>frame_stack</t>
+          <t>hidden1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>hidden1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
         </is>
@@ -2515,69 +1770,66 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6803333333333333</v>
+        <v>0.68104</v>
       </c>
       <c r="B2" t="n">
-        <v>0.007615773105863916</v>
+        <v>0.003998499718644489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6432121666666667</v>
+        <v>0.6570703</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007730363263169178</v>
+        <v>0.004027793431466224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001109309079070013</v>
+        <v>0.0001090049253729382</v>
       </c>
       <c r="F2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="N2" t="n">
-        <v>64</v>
-      </c>
-      <c r="O2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.673</v>
+        <v>0.67299</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009371943946339716</v>
+        <v>0.0009482879309577006</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6266681666666666</v>
+        <v>0.615591075</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008575574029215523</v>
+        <v>0.00105552490866514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001082369313330419</v>
+        <v>0.0005016631968599064</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G3" t="n">
         <v>0.2</v>
@@ -2589,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -2598,45 +1850,42 @@
         <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="N3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O3" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6704666666666667</v>
+        <v>0.67066</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009106163968555698</v>
+        <v>0.002902025154956446</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6179198333333333</v>
+        <v>0.6307564000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008702535099198267</v>
+        <v>0.003072089489459924</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002342281583504994</v>
+        <v>0.0002139331892500008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -2645,124 +1894,115 @@
         <v>64</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="N4" t="n">
-        <v>128</v>
-      </c>
-      <c r="O4" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.6702666666666667</v>
+        <v>0.67049</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00827445869327215</v>
+        <v>0.002764597619907806</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5882746666666666</v>
+        <v>0.6502759499999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00711096970454023</v>
+        <v>0.002756753084189298</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002124581964224018</v>
+        <v>0.002458429052828939</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="N5" t="n">
-        <v>64</v>
-      </c>
-      <c r="O5" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6695333333333334</v>
+        <v>0.6695</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01009840471449713</v>
+        <v>0.004753814258045857</v>
       </c>
       <c r="C6" t="n">
-        <v>0.624738</v>
+        <v>0.6384711000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009930559956098447</v>
+        <v>0.004577596740341795</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003757492064184008</v>
+        <v>0.0001942663440330811</v>
       </c>
       <c r="F6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="n">
         <v>0.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" t="n">
+        <v>128</v>
+      </c>
+      <c r="M6" t="n">
         <v>256</v>
       </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
       <c r="N6" t="n">
-        <v>256</v>
-      </c>
-      <c r="O6" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.6682</v>
+        <v>0.66584</v>
       </c>
       <c r="B7" t="n">
-        <v>0.006044281043543029</v>
+        <v>0.001262636131274552</v>
       </c>
       <c r="C7" t="n">
-        <v>0.633446</v>
+        <v>0.6015031000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006169722593034497</v>
+        <v>0.001553581918201474</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001109309079070013</v>
+        <v>0.0003574712922600246</v>
       </c>
       <c r="F7" t="n">
         <v>0.9</v>
@@ -2771,7 +2011,7 @@
         <v>0.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -2783,42 +2023,39 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="N7" t="n">
-        <v>64</v>
-      </c>
-      <c r="O7" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.6675333333333333</v>
+        <v>0.6645799999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>0.004598308867882274</v>
+        <v>0.001848512915832613</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5953491666666667</v>
+        <v>0.6002341249999998</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005142094221823548</v>
+        <v>0.001611237899973937</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000117115099555241</v>
+        <v>0.0003384522041201141</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I8" t="n">
         <v>0.5</v>
@@ -2830,39 +2067,36 @@
         <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="N8" t="n">
         <v>64</v>
       </c>
-      <c r="O8" t="n">
-        <v>64</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.6646666666666667</v>
+        <v>0.66428</v>
       </c>
       <c r="B9" t="n">
-        <v>0.007039570693980959</v>
+        <v>0.001091787525116506</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5720886666666667</v>
+        <v>0.602361475</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005826910916886673</v>
+        <v>0.001612285526919065</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003</v>
+        <v>0.0001972161097057403</v>
       </c>
       <c r="F9" t="n">
         <v>0.95</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="n">
         <v>0.01</v>
@@ -2871,142 +2105,133 @@
         <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>256</v>
       </c>
       <c r="N9" t="n">
-        <v>128</v>
-      </c>
-      <c r="O9" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.6644</v>
+        <v>0.66386</v>
       </c>
       <c r="B10" t="n">
-        <v>0.004335896677735775</v>
+        <v>0.004855589562555722</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5836666666666667</v>
+        <v>0.570147575</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006303175318616966</v>
+        <v>0.004779101533303631</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002900210932479527</v>
+        <v>0.002442046084491142</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="N10" t="n">
-        <v>64</v>
-      </c>
-      <c r="O10" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.6644</v>
+        <v>0.6623899999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004335896677735775</v>
+        <v>0.005890394723615747</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5836666666666667</v>
+        <v>0.5933355</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006303175318616966</v>
+        <v>0.006086366272123092</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002900210932479527</v>
+        <v>0.0004841041099321571</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="n">
         <v>0.05</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>512</v>
+        <v>2048</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
+        <v>128</v>
+      </c>
+      <c r="M11" t="n">
         <v>256</v>
       </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
       <c r="N11" t="n">
-        <v>64</v>
-      </c>
-      <c r="O11" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.6639333333333334</v>
+        <v>0.66179</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01133921416050418</v>
+        <v>0.001933067510461044</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6254233333333333</v>
+        <v>0.59518465</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01128825989505618</v>
+        <v>0.001859650568655343</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0002342281583504994</v>
+        <v>0.0002710864828729778</v>
       </c>
       <c r="F12" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -3018,39 +2243,36 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="N12" t="n">
-        <v>128</v>
-      </c>
-      <c r="O12" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6636000000000001</v>
+        <v>0.66042</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008920637745014517</v>
+        <v>0.003005328601001914</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5950810000000001</v>
+        <v>0.6072523750000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01001351977398003</v>
+        <v>0.002941978394720083</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0001082369313330419</v>
+        <v>0.0003571439909823144</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H13" t="n">
         <v>0.01</v>
@@ -3062,83 +2284,77 @@
         <v>1024</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>256</v>
       </c>
       <c r="N13" t="n">
-        <v>128</v>
-      </c>
-      <c r="O13" t="n">
         <v>256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.6631333333333334</v>
+        <v>0.66025</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01214633003558415</v>
+        <v>0.003265539771615085</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6085526666666666</v>
+        <v>0.583343425</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01201604825905299</v>
+        <v>0.003151468564663499</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001133669581784054</v>
+        <v>0.0004872420129560896</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H14" t="n">
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>512</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="N14" t="n">
-        <v>64</v>
-      </c>
-      <c r="O14" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6626666666666667</v>
+        <v>0.6593600000000001</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009935905707192601</v>
+        <v>0.002730247241551576</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6141163333333333</v>
+        <v>0.597537175</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00964585530235074</v>
+        <v>0.002533574563178996</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0003574712922600246</v>
+        <v>0.002322119672134761</v>
       </c>
       <c r="F15" t="n">
         <v>0.9</v>
@@ -3147,57 +2363,54 @@
         <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>512</v>
+        <v>2048</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="N15" t="n">
         <v>256</v>
       </c>
-      <c r="O15" t="n">
-        <v>256</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6622</v>
+        <v>0.6576299999999999</v>
       </c>
       <c r="B16" t="n">
-        <v>0.004891034882539889</v>
+        <v>0.002307758652892452</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5890845</v>
+        <v>0.5814560249999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005018465921806476</v>
+        <v>0.002441439360615512</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000874479618932312</v>
+        <v>0.002190714227215282</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>2048</v>
@@ -3209,130 +2422,121 @@
         <v>64</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="N16" t="n">
-        <v>256</v>
-      </c>
-      <c r="O16" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6559</v>
       </c>
       <c r="B17" t="n">
-        <v>0.006176118881987661</v>
+        <v>0.004430575583375123</v>
       </c>
       <c r="C17" t="n">
-        <v>0.573807</v>
+        <v>0.56279985</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00449175790723655</v>
+        <v>0.004397363915070263</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0003757492064184008</v>
+        <v>0.0009836162684900027</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>2048</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="N17" t="n">
-        <v>256</v>
-      </c>
-      <c r="O17" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.6616666666666666</v>
+        <v>0.65571</v>
       </c>
       <c r="B18" t="n">
-        <v>0.008806563209081967</v>
+        <v>0.003030965192805736</v>
       </c>
       <c r="C18" t="n">
-        <v>0.58033</v>
+        <v>0.5998882</v>
       </c>
       <c r="D18" t="n">
-        <v>0.009765279196099692</v>
+        <v>0.003235013917087529</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000117115099555241</v>
+        <v>0.0008099164993582627</v>
       </c>
       <c r="F18" t="n">
         <v>0.9</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="N18" t="n">
-        <v>64</v>
-      </c>
-      <c r="O18" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6552899999999999</v>
       </c>
       <c r="B19" t="n">
-        <v>0.008351979140033534</v>
+        <v>0.003497034457937199</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5491064999999999</v>
+        <v>0.5820137</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0067540817751194</v>
+        <v>0.003319088061407057</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001538583627271403</v>
+        <v>0.0001017364485544502</v>
       </c>
       <c r="F19" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H19" t="n">
         <v>0.05</v>
@@ -3341,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
@@ -3350,92 +2554,86 @@
         <v>128</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="N19" t="n">
-        <v>64</v>
-      </c>
-      <c r="O19" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6593333333333333</v>
+        <v>0.6546200000000001</v>
       </c>
       <c r="B20" t="n">
-        <v>0.008618455649231922</v>
+        <v>0.001597889232706723</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6154338333333333</v>
+        <v>0.5613403</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008772310101329591</v>
+        <v>0.002000707743134331</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0001109309079070013</v>
+        <v>0.002904665979638735</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
       </c>
       <c r="L20" t="n">
+        <v>128</v>
+      </c>
+      <c r="M20" t="n">
         <v>256</v>
       </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
       <c r="N20" t="n">
-        <v>64</v>
-      </c>
-      <c r="O20" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.6592666666666667</v>
+        <v>0.65432</v>
       </c>
       <c r="B21" t="n">
-        <v>0.007882470002057326</v>
+        <v>0.003275209916936589</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5784483333333333</v>
+        <v>0.572292575</v>
       </c>
       <c r="D21" t="n">
-        <v>0.007819880424988049</v>
+        <v>0.002957689557798846</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00129667438075127</v>
+        <v>0.0004135867955263891</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I21" t="n">
         <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K21" t="n">
         <v>10</v>
@@ -3444,482 +2642,9 @@
         <v>64</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="N21" t="n">
-        <v>256</v>
-      </c>
-      <c r="O21" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.6591333333333333</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.009263428690885004</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.5703053333333334</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.00877748537531608</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.0007114706514580523</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1024</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" t="n">
-        <v>64</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>128</v>
-      </c>
-      <c r="O22" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0.6587333333333334</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.006197669813011292</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.6148416666666667</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.005131588312707029</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.0008974255743856962</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>512</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>128</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>64</v>
-      </c>
-      <c r="O23" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.6574000000000001</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.006043361831151793</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.6001983333333334</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.006146507222941039</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0001082369313330419</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>512</v>
-      </c>
-      <c r="K24" t="n">
-        <v>10</v>
-      </c>
-      <c r="L24" t="n">
-        <v>128</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>128</v>
-      </c>
-      <c r="O24" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0.6568666666666667</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.007274766128352315</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.6066775</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.007711554214474369</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.000116628902739314</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>512</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>128</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>64</v>
-      </c>
-      <c r="O25" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0.6562666666666667</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.004974378799854757</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.5849096666666667</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.004568320245025632</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0003575594457014808</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1024</v>
-      </c>
-      <c r="K26" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" t="n">
-        <v>128</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>256</v>
-      </c>
-      <c r="O26" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0.6559333333333334</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.008961026726887948</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.5798715000000001</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.01031180587562947</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.0001082369313330419</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1024</v>
-      </c>
-      <c r="K27" t="n">
-        <v>10</v>
-      </c>
-      <c r="L27" t="n">
-        <v>128</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>128</v>
-      </c>
-      <c r="O27" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0.6527999999999999</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.00856219078922627</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5459661666666668</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.008816770175038256</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.000874479618932312</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>512</v>
-      </c>
-      <c r="K28" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" t="n">
-        <v>64</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>256</v>
-      </c>
-      <c r="O28" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0.6516666666666666</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.002121320343559636</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.5808126666666666</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.001536305927469466</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.0003575594457014808</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>512</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>64</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>128</v>
-      </c>
-      <c r="O29" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>0.6504000000000001</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.004889898885571238</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.56786</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.005088590655683666</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.000874479618932312</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2048</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4</v>
-      </c>
-      <c r="L30" t="n">
-        <v>64</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>128</v>
-      </c>
-      <c r="O30" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>0.6476</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.008948618763685143</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.5742735</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.008613421140870825</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.0001133669581784054</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>512</v>
-      </c>
-      <c r="K31" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" t="n">
-        <v>64</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>256</v>
-      </c>
-      <c r="O31" t="n">
         <v>128</v>
       </c>
     </row>
@@ -3964,13 +2689,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.67908</v>
+        <v>0.6617700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.714</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="3">
@@ -3978,13 +2703,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7124200000000001</v>
+        <v>0.69247</v>
       </c>
       <c r="C3" t="n">
-        <v>0.752</v>
+        <v>0.714</v>
       </c>
       <c r="D3" t="n">
-        <v>8.35</v>
+        <v>6.756</v>
       </c>
     </row>
     <row r="4">
@@ -3992,13 +2717,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6599700000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="C4" t="n">
-        <v>0.696</v>
+        <v>0.678</v>
       </c>
       <c r="D4" t="n">
-        <v>8.077999999999999</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="5">
@@ -4006,13 +2731,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6872500000000001</v>
+        <v>0.67884</v>
       </c>
       <c r="C5" t="n">
-        <v>0.724</v>
+        <v>0.704</v>
       </c>
       <c r="D5" t="n">
-        <v>8.02</v>
+        <v>7.852</v>
       </c>
     </row>
     <row r="6">
@@ -4020,13 +2745,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.62602</v>
+        <v>0.654675</v>
       </c>
       <c r="C6" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="D6" t="n">
-        <v>7.426</v>
+        <v>7.508</v>
       </c>
     </row>
   </sheetData>
@@ -4070,13 +2795,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.644815</v>
+        <v>0.63462</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="D2" t="n">
-        <v>8.144</v>
+        <v>7.154</v>
       </c>
     </row>
     <row r="3">
@@ -4084,13 +2809,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.642595</v>
+        <v>0.6642950000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>8.304</v>
+        <v>7.184</v>
       </c>
     </row>
     <row r="4">
@@ -4098,13 +2823,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6599700000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="C4" t="n">
-        <v>0.696</v>
+        <v>0.678</v>
       </c>
       <c r="D4" t="n">
-        <v>8.077999999999999</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="5">
@@ -4112,13 +2837,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.669585</v>
+        <v>0.64834</v>
       </c>
       <c r="C5" t="n">
-        <v>0.708</v>
+        <v>0.674</v>
       </c>
       <c r="D5" t="n">
-        <v>8.273999999999999</v>
+        <v>7.772</v>
       </c>
     </row>
     <row r="6">
@@ -4126,13 +2851,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.66203</v>
+        <v>0.626445</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7</v>
+        <v>0.652</v>
       </c>
       <c r="D6" t="n">
-        <v>8.256</v>
+        <v>7.652</v>
       </c>
     </row>
   </sheetData>
@@ -4176,13 +2901,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6820350000000001</v>
+        <v>0.681065</v>
       </c>
       <c r="C2" t="n">
-        <v>0.724</v>
+        <v>0.708</v>
       </c>
       <c r="D2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="3">
@@ -4190,13 +2915,13 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6546150000000001</v>
+        <v>0.67477</v>
       </c>
       <c r="C3" t="n">
-        <v>0.694</v>
+        <v>0.702</v>
       </c>
       <c r="D3" t="n">
-        <v>8.036</v>
+        <v>8.013999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -4204,13 +2929,13 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6599700000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="C4" t="n">
-        <v>0.696</v>
+        <v>0.678</v>
       </c>
       <c r="D4" t="n">
-        <v>8.077999999999999</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="5">
@@ -4218,13 +2943,13 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5724900000000001</v>
+        <v>0.6161500000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.606</v>
+        <v>0.638</v>
       </c>
       <c r="D5" t="n">
-        <v>7.246</v>
+        <v>6.706</v>
       </c>
     </row>
     <row r="6">
@@ -4232,13 +2957,13 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.47761</v>
+        <v>0.51127</v>
       </c>
       <c r="C6" t="n">
-        <v>0.506</v>
+        <v>0.532</v>
       </c>
       <c r="D6" t="n">
-        <v>5.91</v>
+        <v>6.072</v>
       </c>
     </row>
   </sheetData>

--- a/sepsis_project - Students Version/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/ddqn_ppo_results.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overall Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DDQN Pareto" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PPO Pareto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DDQN Trials" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PPO Trials" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Noise Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Missing Analysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Event Analysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDQN Pareto" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPO Pareto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDQN Trials" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPO Trials" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noise Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Analysis" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,67 +448,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Mean Return Std</t>
+          <t>Survival Rate</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Survival Rate</t>
+          <t>Training Episodes</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Survival Rate Std</t>
+          <t>buffer_size</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Mean Length</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Mean Length Std</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Training Episodes</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Eval Seeds</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Eval Episodes / Seed</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Best Trial</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Best Checkpoint Episode</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Checkpoint Survival</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Checkpoint Return</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>buffer_size</t>
+          <t>target_update_freq</t>
         </is>
       </c>
     </row>
@@ -519,57 +474,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.56438975</v>
+        <v>0.5617217499999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00189883667511186</v>
+        <v>0.65454</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6569199999999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.002203576638104502</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -582,46 +500,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6149963749999999</v>
+        <v>0.6009</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004336154644562683</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6648000000000001</v>
+        <v>50000</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004428741356186892</v>
+        <v>100000</v>
       </c>
       <c r="F3" t="n">
-        <v>7.93232</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.04284701856605676</v>
-      </c>
-      <c r="H3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.6624000000000001</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.6134309999999999</v>
-      </c>
-      <c r="O3" t="n">
-        <v>10000</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -631,45 +522,20 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6570703</v>
+        <v>0.644</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004027793431466224</v>
+        <v>0.67</v>
       </c>
       <c r="D4" t="n">
-        <v>0.68104</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.003998499718644489</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7.35084</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.04251423879125683</v>
-      </c>
-      <c r="H4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.6916</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.6679980000000001</v>
-      </c>
-      <c r="O4" t="inlineStr">
+        <v>50000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A (on-policy)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>N/A (on-policy)</t>
         </is>
@@ -686,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,50 +563,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>survival_rate_std</t>
+          <t>mean_return</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_return</t>
+          <t>net_arch</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_return_std</t>
+          <t>lr</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>net_arch</t>
+          <t>exploration_fraction</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lr</t>
+          <t>epsilon_min</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>exploration_fraction</t>
+          <t>batch_size</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>epsilon_min</t>
+          <t>buffer_size</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>batch_size</t>
+          <t>target_update_freq</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>buffer_size</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>gradient_steps</t>
         </is>
@@ -748,36 +609,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6648000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004428741356186892</v>
+        <v>0.6415150000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6149963749999999</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004336154644562683</v>
+        <v>0.000267775333103133</v>
       </c>
       <c r="E2" t="n">
-        <v>128</v>
+        <v>0.05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001040166367988732</v>
+        <v>0.05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>128</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>100000</v>
       </c>
       <c r="I2" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -792,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,65 +661,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>survival_rate_std</t>
+          <t>mean_return</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_return</t>
+          <t>lr</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_return_std</t>
+          <t>gae_lambda</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>lr</t>
+          <t>clip_eps</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>gae_lambda</t>
+          <t>entropy_coef</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>clip_eps</t>
+          <t>value_coef</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>entropy_coef</t>
+          <t>rollout_length</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>value_coef</t>
+          <t>update_epochs</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>rollout_length</t>
+          <t>minibatch_size</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>update_epochs</t>
+          <t>hidden1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>minibatch_size</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>hidden1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
         </is>
@@ -869,45 +717,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.68104</v>
+        <v>0.714</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003998499718644489</v>
+        <v>0.6570900000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6570703</v>
+        <v>0.0001090049253729382</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004027793431466224</v>
+        <v>0.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001090049253729382</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05</v>
+        <v>512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="L2" t="n">
-        <v>256</v>
-      </c>
-      <c r="M2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N2" t="n">
         <v>128</v>
       </c>
     </row>
@@ -922,764 +764,699 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>net_arch</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lr</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>exploration_fraction</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>epsilon_min</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>batch_size</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>buffer_size</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>target_update_freq</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gradient_steps</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>survival_rate</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>survival_rate_std</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mean_return</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mean_return_std</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>net_arch</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lr</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>exploration_fraction</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>epsilon_min</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>batch_size</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>buffer_size</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>gradient_steps</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6648000000000001</v>
+        <v>128</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004428741356186892</v>
+        <v>0.000267775333103133</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6149963749999999</v>
+        <v>0.05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004336154644562683</v>
+        <v>0.05</v>
       </c>
       <c r="E2" t="n">
         <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001040166367988732</v>
+        <v>100000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>64</v>
+        <v>0.732</v>
       </c>
       <c r="J2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
+        <v>0.6415150000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6645800000000001</v>
+        <v>256</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003255495354012994</v>
+        <v>0.0008775452610882307</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6134201000000001</v>
+        <v>0.05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003635447710779564</v>
+        <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001190201204959624</v>
+        <v>10000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2</v>
+        <v>500</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>32</v>
+        <v>0.698</v>
       </c>
       <c r="J3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
+        <v>0.6303650000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.65984</v>
+        <v>64</v>
       </c>
       <c r="B4" t="n">
-        <v>0.004104174703883874</v>
+        <v>0.0008556226023737445</v>
       </c>
       <c r="C4" t="n">
-        <v>0.560249475</v>
+        <v>0.05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004116016941663689</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00397667839903973</v>
+        <v>10000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>500</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>128</v>
+        <v>0.696</v>
       </c>
       <c r="J4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
+        <v>0.611435</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.6593600000000001</v>
+        <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>0.004635380243302586</v>
+        <v>0.0001073886382247958</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5688668750000001</v>
+        <v>0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004179748606562636</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000714439313109744</v>
+        <v>100000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>128</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
+        <v>0.597415</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6577999999999999</v>
+        <v>64</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004344968354315121</v>
+        <v>0.0003617355603250917</v>
       </c>
       <c r="C6" t="n">
-        <v>0.558401275</v>
+        <v>0.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004169584052059305</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0004574578205475404</v>
+        <v>10000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>128</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+        <v>0.6112000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.65759</v>
+        <v>256</v>
       </c>
       <c r="B7" t="n">
-        <v>0.004451179618932517</v>
+        <v>0.0008289395383720047</v>
       </c>
       <c r="C7" t="n">
-        <v>0.54107985</v>
+        <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004275967256620135</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001281334807364802</v>
+        <v>50000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>32</v>
+        <v>0.68</v>
       </c>
       <c r="J7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
+        <v>0.59111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.6572800000000001</v>
+        <v>128</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001830505394692945</v>
+        <v>0.0001423638128723575</v>
       </c>
       <c r="C8" t="n">
-        <v>0.57401685</v>
+        <v>0.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001733797508361386</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
         <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000316417019548443</v>
+        <v>100000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>32</v>
+        <v>0.68</v>
       </c>
       <c r="J8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
+        <v>0.58221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.65725</v>
+        <v>64</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001432654878189446</v>
+        <v>0.002249198965267357</v>
       </c>
       <c r="C9" t="n">
-        <v>0.575302975</v>
+        <v>0.05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001710698693151393</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003135775732257748</v>
+        <v>10000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>64</v>
+        <v>0.678</v>
       </c>
       <c r="J9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+        <v>0.6070050000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.65712</v>
+        <v>256</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002935685609870385</v>
+        <v>0.0002183935292318299</v>
       </c>
       <c r="C10" t="n">
-        <v>0.55711575</v>
+        <v>0.1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003401699950713934</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0007610438922351127</v>
+        <v>100000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2</v>
+        <v>250</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>32</v>
+        <v>0.676</v>
       </c>
       <c r="J10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
+        <v>0.594685</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.6561600000000001</v>
+        <v>64</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001404635183953495</v>
+        <v>0.003284210350911732</v>
       </c>
       <c r="C11" t="n">
-        <v>0.52013205</v>
+        <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0007560516609746166</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
         <v>128</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0003153579159668694</v>
+        <v>50000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>500</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>32</v>
+        <v>0.67</v>
       </c>
       <c r="J11" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
+        <v>0.6179049999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.6551100000000001</v>
+        <v>256</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002957913115694912</v>
+        <v>0.003894923038838411</v>
       </c>
       <c r="C12" t="n">
-        <v>0.552511875</v>
+        <v>0.05</v>
       </c>
       <c r="D12" t="n">
-        <v>0.002632115987245345</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0002074803317589487</v>
+        <v>50000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>128</v>
+        <v>0.67</v>
       </c>
       <c r="J12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
+        <v>0.6052249999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.65505</v>
+        <v>64</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006248499819956788</v>
+        <v>0.0001393595487688128</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5322492999999999</v>
+        <v>0.05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005666194542939547</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0008746431657116674</v>
+        <v>10000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>0.668</v>
       </c>
       <c r="J13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
+        <v>0.5999100000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.6545300000000001</v>
+        <v>64</v>
       </c>
       <c r="B14" t="n">
-        <v>0.006243356469079743</v>
+        <v>0.0001021837675800809</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5517352250000001</v>
+        <v>0.05</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005832954921178442</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00124775471175797</v>
+        <v>10000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>500</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>64</v>
+        <v>0.664</v>
       </c>
       <c r="J14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+        <v>0.58724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6538700000000001</v>
+        <v>128</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003141576037596425</v>
+        <v>0.001040166367988732</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5442390500000001</v>
+        <v>0.05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002914186320559754</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000353747484467483</v>
+        <v>10000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>0.66</v>
       </c>
       <c r="J15" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
+        <v>0.593585</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.65374</v>
+        <v>256</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001945957347939582</v>
+        <v>0.0006901506581791928</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5501119750000001</v>
+        <v>0.05</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001278760946311857</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
         <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001104552426030473</v>
+        <v>100000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>250</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>128</v>
+        <v>0.66</v>
       </c>
       <c r="J16" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
+        <v>0.578865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.65364</v>
+        <v>128</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003791503659499751</v>
+        <v>0.0004329677966181864</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5561039250000001</v>
+        <v>0.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003377297938302532</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>256</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0002577772852685678</v>
+        <v>10000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>500</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>0.656</v>
       </c>
       <c r="J17" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
+        <v>0.573175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.65341</v>
+        <v>256</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003222072314520558</v>
+        <v>0.0003793280795162164</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5989162</v>
+        <v>0.05</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003187032069329921</v>
+        <v>0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00069389014127394</v>
+        <v>50000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>128</v>
+        <v>0.65</v>
       </c>
       <c r="J18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
+        <v>0.5717850000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.6527399999999999</v>
+        <v>256</v>
       </c>
       <c r="B19" t="n">
-        <v>0.002235900266112059</v>
+        <v>0.0002060924941320236</v>
       </c>
       <c r="C19" t="n">
-        <v>0.548358225</v>
+        <v>0.05</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001796039987288008</v>
+        <v>0.1</v>
       </c>
       <c r="E19" t="n">
         <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0001573468512939367</v>
+        <v>50000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>128</v>
+        <v>0.648</v>
       </c>
       <c r="J19" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
+        <v>0.563585</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6518699999999999</v>
+        <v>64</v>
       </c>
       <c r="B20" t="n">
-        <v>0.003700439163126457</v>
+        <v>0.0006867090776580455</v>
       </c>
       <c r="C20" t="n">
-        <v>0.56084225</v>
+        <v>0.1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003368400435249298</v>
+        <v>0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0003067785513876972</v>
+        <v>100000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>64</v>
+        <v>0.648</v>
       </c>
       <c r="J20" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
+        <v>0.54827</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.65051</v>
+        <v>256</v>
       </c>
       <c r="B21" t="n">
-        <v>0.002152150087702971</v>
+        <v>0.001793348639944684</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5566139</v>
+        <v>0.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002556643671398082</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001112527727653784</v>
+        <v>50000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05</v>
+        <v>250</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>32</v>
+        <v>0.646</v>
       </c>
       <c r="J21" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+        <v>0.579495</v>
       </c>
     </row>
   </sheetData>
@@ -1693,959 +1470,829 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>lr</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>gae_lambda</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>clip_eps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>entropy_coef</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>value_coef</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rollout_length</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>update_epochs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>minibatch_size</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>hidden1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>hidden2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>survival_rate</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>survival_rate_std</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mean_return</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mean_return_std</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>lr</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>gae_lambda</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>clip_eps</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>entropy_coef</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>value_coef</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>rollout_length</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>update_epochs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>minibatch_size</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>hidden1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>hidden2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.68104</v>
+        <v>0.0001090049253729382</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003998499718644489</v>
+        <v>0.9</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6570703</v>
+        <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004027793431466224</v>
+        <v>0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001090049253729382</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05</v>
+        <v>256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>128</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>0.714</v>
       </c>
       <c r="L2" t="n">
-        <v>256</v>
-      </c>
-      <c r="M2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N2" t="n">
-        <v>128</v>
+        <v>0.6570900000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.67299</v>
+        <v>0.002190714227215282</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009482879309577006</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.615591075</v>
+        <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00105552490866514</v>
+        <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005016631968599064</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.95</v>
+        <v>2048</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>64</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="J3" t="n">
-        <v>1024</v>
+        <v>64</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>0.696</v>
       </c>
       <c r="L3" t="n">
-        <v>64</v>
-      </c>
-      <c r="M3" t="n">
-        <v>64</v>
-      </c>
-      <c r="N3" t="n">
-        <v>64</v>
+        <v>0.6093699999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.67066</v>
+        <v>0.0005016631968599064</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002902025154956446</v>
+        <v>0.95</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6307564000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003072089489459924</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002139331892500008</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1024</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>1024</v>
+        <v>64</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>64</v>
-      </c>
-      <c r="M4" t="n">
-        <v>64</v>
-      </c>
-      <c r="N4" t="n">
-        <v>64</v>
+        <v>0.635455</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.67049</v>
+        <v>0.0003574712922600246</v>
       </c>
       <c r="B5" t="n">
-        <v>0.002764597619907806</v>
+        <v>0.9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6502759499999999</v>
+        <v>0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002756753084189298</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002458429052828939</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.95</v>
+        <v>512</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>64</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J5" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>256</v>
-      </c>
-      <c r="M5" t="n">
-        <v>128</v>
-      </c>
-      <c r="N5" t="n">
-        <v>256</v>
+        <v>0.62287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6695</v>
+        <v>0.002442046084491142</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004753814258045857</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6384711000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004577596740341795</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001942663440330811</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>1024</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="J6" t="n">
-        <v>1024</v>
+        <v>128</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>128</v>
-      </c>
-      <c r="M6" t="n">
-        <v>256</v>
-      </c>
-      <c r="N6" t="n">
-        <v>64</v>
+        <v>0.59914</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.66584</v>
+        <v>0.0009836162684900027</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001262636131274552</v>
+        <v>0.9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6015031000000001</v>
+        <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001553581918201474</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003574712922600246</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>2048</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="J7" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>64</v>
-      </c>
-      <c r="M7" t="n">
-        <v>64</v>
-      </c>
-      <c r="N7" t="n">
-        <v>256</v>
+        <v>0.5915750000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.6645799999999999</v>
+        <v>0.0002710864828729778</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001848512915832613</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6002341249999998</v>
+        <v>0.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001611237899973937</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003384522041201141</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.95</v>
+        <v>512</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01</v>
+        <v>256</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>128</v>
       </c>
       <c r="J8" t="n">
-        <v>2048</v>
+        <v>256</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>0.68</v>
       </c>
       <c r="L8" t="n">
-        <v>128</v>
-      </c>
-      <c r="M8" t="n">
-        <v>128</v>
-      </c>
-      <c r="N8" t="n">
-        <v>64</v>
+        <v>0.6042649999999998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.66428</v>
+        <v>0.002904665979638735</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001091787525116506</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.602361475</v>
+        <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001612285526919065</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001972161097057403</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.95</v>
+        <v>1024</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01</v>
+        <v>128</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>256</v>
       </c>
       <c r="J9" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0.678</v>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
-      </c>
-      <c r="M9" t="n">
-        <v>256</v>
-      </c>
-      <c r="N9" t="n">
-        <v>128</v>
+        <v>0.606115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.66386</v>
+        <v>0.0004872420129560896</v>
       </c>
       <c r="B10" t="n">
-        <v>0.004855589562555722</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.570147575</v>
+        <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004779101533303631</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002442046084491142</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01</v>
+        <v>256</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>256</v>
       </c>
       <c r="J10" t="n">
-        <v>1024</v>
+        <v>128</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>0.678</v>
       </c>
       <c r="L10" t="n">
-        <v>64</v>
-      </c>
-      <c r="M10" t="n">
-        <v>128</v>
-      </c>
-      <c r="N10" t="n">
-        <v>128</v>
+        <v>0.5858949999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.6623899999999999</v>
+        <v>0.0001017364485544502</v>
       </c>
       <c r="B11" t="n">
-        <v>0.005890394723615747</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5933355</v>
+        <v>0.3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006086366272123092</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0004841041099321571</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.95</v>
+        <v>512</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05</v>
+        <v>128</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="J11" t="n">
-        <v>2048</v>
+        <v>128</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>0.676</v>
       </c>
       <c r="L11" t="n">
-        <v>128</v>
-      </c>
-      <c r="M11" t="n">
-        <v>256</v>
-      </c>
-      <c r="N11" t="n">
-        <v>128</v>
+        <v>0.60956</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.66179</v>
+        <v>0.0004841041099321571</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001933067510461044</v>
+        <v>0.95</v>
       </c>
       <c r="C12" t="n">
-        <v>0.59518465</v>
+        <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001859650568655343</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0002710864828729778</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2048</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>128</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="J12" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>0.672</v>
       </c>
       <c r="L12" t="n">
-        <v>256</v>
-      </c>
-      <c r="M12" t="n">
-        <v>128</v>
-      </c>
-      <c r="N12" t="n">
-        <v>256</v>
+        <v>0.5932999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.66042</v>
+        <v>0.0004135867955263891</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003005328601001914</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6072523750000001</v>
+        <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002941978394720083</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0003571439909823144</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01</v>
+        <v>64</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J13" t="n">
-        <v>1024</v>
+        <v>128</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>0.668</v>
       </c>
       <c r="L13" t="n">
-        <v>256</v>
-      </c>
-      <c r="M13" t="n">
-        <v>256</v>
-      </c>
-      <c r="N13" t="n">
-        <v>256</v>
+        <v>0.577765</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.66025</v>
+        <v>0.002322119672134761</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003265539771615085</v>
+        <v>0.9</v>
       </c>
       <c r="C14" t="n">
-        <v>0.583343425</v>
+        <v>0.1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.003151468564663499</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004872420129560896</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2048</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05</v>
+        <v>64</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>128</v>
       </c>
       <c r="J14" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0.664</v>
       </c>
       <c r="L14" t="n">
-        <v>256</v>
-      </c>
-      <c r="M14" t="n">
-        <v>256</v>
-      </c>
-      <c r="N14" t="n">
-        <v>128</v>
+        <v>0.600715</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6593600000000001</v>
+        <v>0.002458429052828939</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002730247241551576</v>
+        <v>0.95</v>
       </c>
       <c r="C15" t="n">
-        <v>0.597537175</v>
+        <v>0.1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002533574563178996</v>
+        <v>0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002322119672134761</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>512</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05</v>
+        <v>256</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>128</v>
       </c>
       <c r="J15" t="n">
-        <v>2048</v>
+        <v>256</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0.664</v>
       </c>
       <c r="L15" t="n">
-        <v>64</v>
-      </c>
-      <c r="M15" t="n">
-        <v>128</v>
-      </c>
-      <c r="N15" t="n">
-        <v>256</v>
+        <v>0.5836950000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6576299999999999</v>
+        <v>0.0008099164993582627</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002307758652892452</v>
+        <v>0.9</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5814560249999999</v>
+        <v>0.1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002441439360615512</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002190714227215282</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1024</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>256</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J16" t="n">
-        <v>2048</v>
+        <v>128</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>0.662</v>
       </c>
       <c r="L16" t="n">
-        <v>64</v>
-      </c>
-      <c r="M16" t="n">
-        <v>256</v>
-      </c>
-      <c r="N16" t="n">
-        <v>64</v>
+        <v>0.6012999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6559</v>
+        <v>0.0003571439909823144</v>
       </c>
       <c r="B17" t="n">
-        <v>0.004430575583375123</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.56279985</v>
+        <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004397363915070263</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0009836162684900027</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>1024</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05</v>
+        <v>256</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>256</v>
       </c>
       <c r="J17" t="n">
-        <v>2048</v>
+        <v>256</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>0.648</v>
       </c>
       <c r="L17" t="n">
-        <v>128</v>
-      </c>
-      <c r="M17" t="n">
-        <v>256</v>
-      </c>
-      <c r="N17" t="n">
-        <v>128</v>
+        <v>0.58956</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.65571</v>
+        <v>0.0002139331892500008</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003030965192805736</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5998882</v>
+        <v>0.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003235013917087529</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0008099164993582627</v>
+        <v>0.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9</v>
+        <v>1024</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>1024</v>
+        <v>64</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>0.64</v>
       </c>
       <c r="L18" t="n">
-        <v>256</v>
-      </c>
-      <c r="M18" t="n">
-        <v>64</v>
-      </c>
-      <c r="N18" t="n">
-        <v>128</v>
+        <v>0.599205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.6552899999999999</v>
+        <v>0.0001942663440330811</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003497034457937199</v>
+        <v>0.9</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5820137</v>
+        <v>0.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003319088061407057</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0001017364485544502</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1024</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05</v>
+        <v>128</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="J19" t="n">
-        <v>512</v>
+        <v>64</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>0.634</v>
       </c>
       <c r="L19" t="n">
-        <v>128</v>
-      </c>
-      <c r="M19" t="n">
-        <v>64</v>
-      </c>
-      <c r="N19" t="n">
-        <v>128</v>
+        <v>0.6012900000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6546200000000001</v>
+        <v>0.0003384522041201141</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001597889232706723</v>
+        <v>0.95</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5613403</v>
+        <v>0.1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002000707743134331</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002904665979638735</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2048</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05</v>
+        <v>128</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="J20" t="n">
-        <v>1024</v>
+        <v>64</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>0.626</v>
       </c>
       <c r="L20" t="n">
-        <v>128</v>
-      </c>
-      <c r="M20" t="n">
-        <v>256</v>
-      </c>
-      <c r="N20" t="n">
-        <v>128</v>
+        <v>0.5481549999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.65432</v>
+        <v>0.0001972161097057403</v>
       </c>
       <c r="B21" t="n">
-        <v>0.003275209916936589</v>
+        <v>0.95</v>
       </c>
       <c r="C21" t="n">
-        <v>0.572292575</v>
+        <v>0.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002957689557798846</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0004135867955263891</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05</v>
+        <v>64</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>256</v>
       </c>
       <c r="J21" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>0.622</v>
       </c>
       <c r="L21" t="n">
-        <v>64</v>
-      </c>
-      <c r="M21" t="n">
-        <v>64</v>
-      </c>
-      <c r="N21" t="n">
-        <v>128</v>
+        <v>0.55403</v>
       </c>
     </row>
   </sheetData>
@@ -2689,13 +2336,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6617700000000001</v>
+        <v>0.602185</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="D2" t="n">
-        <v>6.972</v>
+        <v>9.324</v>
       </c>
     </row>
     <row r="3">
@@ -2703,13 +2350,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.69247</v>
+        <v>0.5773400000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.714</v>
+        <v>0.66</v>
       </c>
       <c r="D3" t="n">
-        <v>6.756</v>
+        <v>9.811999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2717,13 +2364,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6544</v>
+        <v>0.606115</v>
       </c>
       <c r="C4" t="n">
-        <v>0.678</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>7.37</v>
+        <v>9.545999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2731,13 +2378,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.67884</v>
+        <v>0.574755</v>
       </c>
       <c r="C5" t="n">
-        <v>0.704</v>
+        <v>0.654</v>
       </c>
       <c r="D5" t="n">
-        <v>7.852</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="6">
@@ -2745,13 +2392,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.654675</v>
+        <v>0.5856549999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="D6" t="n">
-        <v>7.508</v>
+        <v>10.486</v>
       </c>
     </row>
   </sheetData>
@@ -2795,13 +2442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.63462</v>
+        <v>0.5934349999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.658</v>
+        <v>0.672</v>
       </c>
       <c r="D2" t="n">
-        <v>7.154</v>
+        <v>9.496</v>
       </c>
     </row>
     <row r="3">
@@ -2809,13 +2456,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6642950000000001</v>
+        <v>0.58701</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>7.184</v>
+        <v>9.938000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2823,13 +2470,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6544</v>
+        <v>0.606115</v>
       </c>
       <c r="C4" t="n">
-        <v>0.678</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>7.37</v>
+        <v>9.545999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2837,13 +2484,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.64834</v>
+        <v>0.6255550000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.674</v>
+        <v>0.71</v>
       </c>
       <c r="D5" t="n">
-        <v>7.772</v>
+        <v>9.972</v>
       </c>
     </row>
     <row r="6">
@@ -2851,13 +2498,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.626445</v>
+        <v>0.577645</v>
       </c>
       <c r="C6" t="n">
-        <v>0.652</v>
+        <v>0.66</v>
       </c>
       <c r="D6" t="n">
-        <v>7.652</v>
+        <v>9.69</v>
       </c>
     </row>
   </sheetData>
@@ -2901,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.681065</v>
+        <v>0.6246700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.708</v>
+        <v>0.718</v>
       </c>
       <c r="D2" t="n">
-        <v>8.17</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="3">
@@ -2915,13 +2562,13 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.67477</v>
+        <v>0.58636</v>
       </c>
       <c r="C3" t="n">
-        <v>0.702</v>
+        <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>8.013999999999999</v>
+        <v>9.832000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2929,13 +2576,13 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6544</v>
+        <v>0.606115</v>
       </c>
       <c r="C4" t="n">
-        <v>0.678</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>7.37</v>
+        <v>9.545999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2943,13 +2590,13 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6161500000000001</v>
+        <v>0.51484</v>
       </c>
       <c r="C5" t="n">
-        <v>0.638</v>
+        <v>0.58</v>
       </c>
       <c r="D5" t="n">
-        <v>6.706</v>
+        <v>7.738</v>
       </c>
     </row>
     <row r="6">
@@ -2957,13 +2604,13 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.51127</v>
+        <v>0.441815</v>
       </c>
       <c r="C6" t="n">
-        <v>0.532</v>
+        <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.072</v>
+        <v>7.09</v>
       </c>
     </row>
   </sheetData>

--- a/sepsis_project - Students Version/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/ddqn_ppo_results.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDQN Pareto" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPO Pareto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDQN Trials" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPO Trials" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noise Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Analysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Analysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Overall Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DDQN Pareto" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PPO Pareto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DDQN Trials" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PPO Trials" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Noise Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Missing Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Event Analysis" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,22 +448,67 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Mean Return Std</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Survival Rate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Rate Std</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Length</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Length Std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Training Episodes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Eval Seeds</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Eval Episodes / Seed</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Best Trial</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Best Checkpoint Episode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Checkpoint Survival</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Checkpoint Return</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>buffer_size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>target_update_freq</t>
         </is>
       </c>
     </row>
@@ -474,20 +519,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5617217499999999</v>
+        <v>0.5617353300000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.65454</v>
+        <v>0.001741650181795975</v>
       </c>
       <c r="D2" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.001697822134382755</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -500,19 +582,44 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6009</v>
+        <v>0.58529392</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.001276281475909574</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6623080000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.001519842097061406</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.149056</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.04235667928438221</v>
+      </c>
+      <c r="H3" t="n">
         <v>50000</v>
       </c>
-      <c r="E3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>50</v>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6164175000000001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="4">
@@ -522,20 +629,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.644</v>
+        <v>0.6112099600000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.67</v>
+        <v>0.002760214481113775</v>
       </c>
       <c r="D4" t="n">
+        <v>0.671772</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.002803875888836743</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.599399999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.02892252755206523</v>
+      </c>
+      <c r="H4" t="n">
         <v>50000</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/A (on-policy)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6366000000000001</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>N/A (on-policy)</t>
         </is>
@@ -552,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,45 +693,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>mean_return</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_arch</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>exploration_fraction</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>epsilon_min</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>buffer_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>target_update_freq</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>gradient_steps</t>
         </is>
@@ -609,34 +749,154 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.732</v>
+        <v>0.67106</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6415150000000001</v>
+        <v>0.002267818334876032</v>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>0.5845651000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000267775333103133</v>
+        <v>0.002414977992912154</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>256</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05</v>
+        <v>0.0003793280795162164</v>
       </c>
       <c r="G2" t="n">
-        <v>128</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
-        <v>100000</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.66956</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.004439369324577513</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.59439245</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.004373219714209405</v>
+      </c>
+      <c r="E3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.002249198965267357</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K3" t="n">
         <v>50</v>
       </c>
-      <c r="J2" t="n">
-        <v>2</v>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.6687</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.002462722071204968</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6060435</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.002333501078047773</v>
+      </c>
+      <c r="E4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0001393595487688128</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.6642600000000001</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.002668894902389395</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6110368500000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.003002137392758689</v>
+      </c>
+      <c r="E5" t="n">
+        <v>256</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.003894923038838411</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>64</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>500</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,55 +921,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>mean_return</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gae_lambda</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>clip_eps</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>entropy_coef</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>value_coef</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rollout_length</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>update_epochs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>minibatch_size</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hidden1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
         </is>
@@ -717,40 +987,90 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.714</v>
+        <v>0.67248</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6570900000000001</v>
+        <v>0.0017852170736356</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001090049253729382</v>
+        <v>0.6112832500000001</v>
       </c>
       <c r="D2" t="n">
+        <v>0.002395016877550071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0005016631968599064</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>64</v>
+      </c>
+      <c r="M2" t="n">
+        <v>64</v>
+      </c>
+      <c r="N2" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.004256171989006086</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6406615500000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.004204624847266416</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0001942663440330811</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>512</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="G3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L3" t="n">
+        <v>128</v>
+      </c>
+      <c r="M3" t="n">
         <v>256</v>
       </c>
-      <c r="K2" t="n">
-        <v>128</v>
-      </c>
-      <c r="L2" t="n">
-        <v>128</v>
+      <c r="N3" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -764,699 +1084,829 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>net_arch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>exploration_fraction</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>epsilon_min</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>buffer_size</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>target_update_freq</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>gradient_steps</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>survival_rate</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>mean_return</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128</v>
+        <v>0.67106</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000267775333103133</v>
+        <v>0.002267818334876032</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05</v>
+        <v>0.5845651000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05</v>
+        <v>0.002414977992912154</v>
       </c>
       <c r="E2" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F2" t="n">
-        <v>100000</v>
+        <v>0.0003793280795162164</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6415150000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>256</v>
+        <v>0.66956</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0008775452610882307</v>
+        <v>0.004439369324577513</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05</v>
+        <v>0.59439245</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>0.004373219714209405</v>
       </c>
       <c r="E3" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
+        <v>0.002249198965267357</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J3" t="n">
         <v>10000</v>
       </c>
-      <c r="G3" t="n">
-        <v>500</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6303650000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>0.6691800000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0008556226023737445</v>
+        <v>0.008939071540154489</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05</v>
+        <v>0.5901411</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>0.008363573259976826</v>
       </c>
       <c r="E4" t="n">
         <v>128</v>
       </c>
       <c r="F4" t="n">
+        <v>0.001040166367988732</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I4" t="n">
+        <v>64</v>
+      </c>
+      <c r="J4" t="n">
         <v>10000</v>
       </c>
-      <c r="G4" t="n">
-        <v>500</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.611435</v>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>0.6687</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0001073886382247958</v>
+        <v>0.002462722071204968</v>
       </c>
       <c r="C5" t="n">
+        <v>0.6060435</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.002333501078047773</v>
+      </c>
+      <c r="E5" t="n">
+        <v>64</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0001393595487688128</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="I5" t="n">
         <v>32</v>
       </c>
-      <c r="F5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.6919999999999999</v>
-      </c>
       <c r="J5" t="n">
-        <v>0.597415</v>
+        <v>10000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>0.66632</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0003617355603250917</v>
+        <v>0.009552591271482331</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>0.5966169</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0.008940947215619796</v>
       </c>
       <c r="E6" t="n">
         <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>10000</v>
+        <v>0.0006867090776580455</v>
       </c>
       <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K6" t="n">
         <v>100</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6112000000000001</v>
+      <c r="L6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>256</v>
+        <v>0.66598</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0008289395383720047</v>
+        <v>0.009825833297995688</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2</v>
+        <v>0.59665405</v>
       </c>
       <c r="D7" t="n">
+        <v>0.0103629926547547</v>
+      </c>
+      <c r="E7" t="n">
+        <v>64</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0001073886382247958</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" t="n">
-        <v>64</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>50</v>
-      </c>
       <c r="H7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>32</v>
+      </c>
+      <c r="J7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" t="n">
         <v>4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.59111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128</v>
+        <v>0.6651</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0001423638128723575</v>
+        <v>0.003287095982778685</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05</v>
+        <v>0.5995361000000001</v>
       </c>
       <c r="D8" t="n">
+        <v>0.003271905778747306</v>
+      </c>
+      <c r="E8" t="n">
+        <v>256</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0002183935292318299</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" t="n">
-        <v>64</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I8" t="n">
+        <v>64</v>
+      </c>
+      <c r="J8" t="n">
         <v>100000</v>
       </c>
-      <c r="G8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.58221</v>
+      <c r="K8" t="n">
+        <v>250</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64</v>
+        <v>0.6642600000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002249198965267357</v>
+        <v>0.002668894902389395</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05</v>
+        <v>0.6110368500000002</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>0.003002137392758689</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F9" t="n">
-        <v>10000</v>
+        <v>0.003894923038838411</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>0.05</v>
       </c>
       <c r="H9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>64</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>500</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6070050000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.004611398920067516</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5865459500000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.004259632955871874</v>
+      </c>
+      <c r="E10" t="n">
         <v>256</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.0002183935292318299</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="F10" t="n">
+        <v>0.0002060924941320236</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E10" t="n">
-        <v>64</v>
-      </c>
-      <c r="F10" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G10" t="n">
-        <v>250</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
       <c r="I10" t="n">
-        <v>0.676</v>
+        <v>64</v>
       </c>
       <c r="J10" t="n">
-        <v>0.594685</v>
+        <v>50000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64</v>
+        <v>0.66304</v>
       </c>
       <c r="B11" t="n">
-        <v>0.003284210350911732</v>
+        <v>0.005359850744190545</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2</v>
+        <v>0.5672457</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.005609517747208714</v>
       </c>
       <c r="E11" t="n">
         <v>128</v>
       </c>
       <c r="F11" t="n">
-        <v>50000</v>
+        <v>0.000267775333103133</v>
       </c>
       <c r="G11" t="n">
-        <v>500</v>
+        <v>0.05</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>0.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.67</v>
+        <v>128</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6179049999999999</v>
+        <v>100000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>256</v>
+        <v>0.66266</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003894923038838411</v>
+        <v>0.005333666656250652</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05</v>
+        <v>0.5859490000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.00468823590223448</v>
       </c>
       <c r="E12" t="n">
         <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>50000</v>
+        <v>0.0001021837675800809</v>
       </c>
       <c r="G12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K12" t="n">
         <v>500</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6052249999999999</v>
+      <c r="L12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>64</v>
+        <v>0.6626200000000001</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0001393595487688128</v>
+        <v>0.003014465126685002</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05</v>
+        <v>0.5785712000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.003875237812863795</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
+        <v>0.0003617355603250917</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>64</v>
+      </c>
+      <c r="J13" t="n">
         <v>10000</v>
       </c>
-      <c r="G13" t="n">
-        <v>50</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.5999100000000001</v>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64</v>
+        <v>0.66218</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0001021837675800809</v>
+        <v>0.003457889529756581</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05</v>
+        <v>0.59072965</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.003281715531737919</v>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="F14" t="n">
+        <v>0.0008775452610882307</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>128</v>
+      </c>
+      <c r="J14" t="n">
         <v>10000</v>
       </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
         <v>500</v>
       </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.58724</v>
+      <c r="L14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>0.6603</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.003112073263919105</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5754878</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.002746062438975113</v>
+      </c>
+      <c r="E15" t="n">
         <v>128</v>
       </c>
-      <c r="B15" t="n">
-        <v>0.001040166367988732</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
+        <v>0.0004329677966181864</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.01</v>
       </c>
-      <c r="E15" t="n">
-        <v>64</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
+        <v>32</v>
+      </c>
+      <c r="J15" t="n">
         <v>10000</v>
       </c>
-      <c r="G15" t="n">
-        <v>100</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.593585</v>
+      <c r="K15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>0.6601399999999999</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.005551846539665871</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5721593</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.005152866506251634</v>
+      </c>
+      <c r="E16" t="n">
         <v>256</v>
       </c>
-      <c r="B16" t="n">
-        <v>0.0006901506581791928</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
+        <v>0.001793348639944684</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.1</v>
       </c>
-      <c r="E16" t="n">
-        <v>128</v>
-      </c>
-      <c r="F16" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>64</v>
+      </c>
+      <c r="J16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K16" t="n">
         <v>250</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.578865</v>
+      <c r="L16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>0.65942</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.002109976303184487</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5727225500000002</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.00243744588657879</v>
+      </c>
+      <c r="E17" t="n">
         <v>128</v>
       </c>
-      <c r="B17" t="n">
-        <v>0.0004329677966181864</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E17" t="n">
-        <v>32</v>
-      </c>
       <c r="F17" t="n">
-        <v>10000</v>
+        <v>0.0001423638128723575</v>
       </c>
       <c r="G17" t="n">
-        <v>500</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>64</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>100</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.573175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>256</v>
+        <v>0.6592</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0003793280795162164</v>
+        <v>0.001387443692551164</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05</v>
+        <v>0.5657745000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05</v>
+        <v>0.001538867410224168</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
+        <v>0.003284210350911732</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I18" t="n">
+        <v>128</v>
+      </c>
+      <c r="J18" t="n">
         <v>50000</v>
       </c>
-      <c r="G18" t="n">
-        <v>100</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.5717850000000001</v>
+      <c r="K18" t="n">
+        <v>500</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>0.65824</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.003655543735205481</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5820421499999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.00354204689939308</v>
+      </c>
+      <c r="E19" t="n">
         <v>256</v>
       </c>
-      <c r="B19" t="n">
-        <v>0.0002060924941320236</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
+        <v>0.0006901506581791928</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.1</v>
       </c>
-      <c r="E19" t="n">
-        <v>64</v>
-      </c>
-      <c r="F19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G19" t="n">
-        <v>50</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
       <c r="I19" t="n">
-        <v>0.648</v>
+        <v>128</v>
       </c>
       <c r="J19" t="n">
-        <v>0.563585</v>
+        <v>100000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>250</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>64</v>
+        <v>0.6575799999999999</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0006867090776580455</v>
+        <v>0.00617673052674307</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1</v>
+        <v>0.5712922499999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.05</v>
+        <v>0.006433704036167646</v>
       </c>
       <c r="E20" t="n">
         <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>100000</v>
+        <v>0.0008556226023737445</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>0.05</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.648</v>
+        <v>128</v>
       </c>
       <c r="J20" t="n">
-        <v>0.54827</v>
+        <v>10000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>500</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>0.6565399999999999</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.003953858874567967</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5803184</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.003689679197606493</v>
+      </c>
+      <c r="E21" t="n">
         <v>256</v>
       </c>
-      <c r="B21" t="n">
-        <v>0.001793348639944684</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="F21" t="n">
+        <v>0.0008289395383720047</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.1</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>64</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
+        <v>64</v>
+      </c>
+      <c r="J21" t="n">
         <v>50000</v>
       </c>
-      <c r="G21" t="n">
-        <v>250</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.579495</v>
+      <c r="K21" t="n">
+        <v>50</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1470,829 +1920,959 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>survival_rate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>survival_rate_std</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_return_std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gae_lambda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>clip_eps</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>entropy_coef</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>value_coef</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rollout_length</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>update_epochs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>minibatch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hidden1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hidden2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>survival_rate</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mean_return</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0001090049253729382</v>
+        <v>0.67248</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9</v>
+        <v>0.0017852170736356</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1</v>
+        <v>0.6112832500000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05</v>
+        <v>0.002395016877550071</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.0005016631968599064</v>
       </c>
       <c r="F2" t="n">
-        <v>512</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>256</v>
-      </c>
-      <c r="I2" t="n">
-        <v>128</v>
-      </c>
-      <c r="J2" t="n">
-        <v>128</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.714</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.6570900000000001</v>
+        <v>64</v>
+      </c>
+      <c r="M2" t="n">
+        <v>64</v>
+      </c>
+      <c r="N2" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002190714227215282</v>
+        <v>0.6712</v>
       </c>
       <c r="B3" t="n">
+        <v>0.004256171989006086</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6406615500000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.004204624847266416</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0001942663440330811</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>64</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>128</v>
+      </c>
+      <c r="M3" t="n">
         <v>256</v>
       </c>
-      <c r="J3" t="n">
-        <v>64</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.6093699999999999</v>
+      <c r="N3" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0005016631968599064</v>
+        <v>0.67008</v>
       </c>
       <c r="B4" t="n">
-        <v>0.95</v>
+        <v>0.004676751008980452</v>
       </c>
       <c r="C4" t="n">
+        <v>0.6299984000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.004720569853047436</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0002139331892500008</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.2</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="n">
         <v>1024</v>
       </c>
-      <c r="G4" t="n">
+      <c r="K4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
-        <v>64</v>
-      </c>
-      <c r="I4" t="n">
-        <v>64</v>
-      </c>
-      <c r="J4" t="n">
-        <v>64</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.635455</v>
+        <v>64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>64</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0003574712922600246</v>
+        <v>0.66988</v>
       </c>
       <c r="B5" t="n">
+        <v>0.003741256473432421</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6107681999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.003682885903065756</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0001090049253729382</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.9</v>
       </c>
-      <c r="C5" t="n">
+      <c r="G5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="n">
         <v>512</v>
       </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>64</v>
-      </c>
-      <c r="I5" t="n">
-        <v>64</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
         <v>256</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.62287</v>
+      <c r="M5" t="n">
+        <v>128</v>
+      </c>
+      <c r="N5" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.002442046084491142</v>
+        <v>0.6652600000000001</v>
       </c>
       <c r="B6" t="n">
+        <v>0.00462903877711131</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.58761665</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.004441216822279659</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0002710864828729778</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1024</v>
-      </c>
       <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>512</v>
+      </c>
+      <c r="K6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>64</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>256</v>
+      </c>
+      <c r="M6" t="n">
         <v>128</v>
       </c>
-      <c r="J6" t="n">
-        <v>128</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.59914</v>
+      <c r="N6" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0009836162684900027</v>
+        <v>0.66362</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9</v>
+        <v>0.006193302834514049</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3</v>
+        <v>0.5990324</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.006406278084328711</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>0.002458429052828939</v>
       </c>
       <c r="F7" t="n">
-        <v>2048</v>
+        <v>0.95</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>512</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>256</v>
+      </c>
+      <c r="M7" t="n">
         <v>128</v>
       </c>
-      <c r="I7" t="n">
+      <c r="N7" t="n">
         <v>256</v>
-      </c>
-      <c r="J7" t="n">
-        <v>128</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5915750000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0002710864828729778</v>
+        <v>0.66306</v>
       </c>
       <c r="B8" t="n">
+        <v>0.004978754864421434</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5836188</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.004590407788938839</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0004872420129560896</v>
+      </c>
+      <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
         <v>512</v>
       </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
         <v>256</v>
       </c>
-      <c r="I8" t="n">
+      <c r="M8" t="n">
+        <v>256</v>
+      </c>
+      <c r="N8" t="n">
         <v>128</v>
-      </c>
-      <c r="J8" t="n">
-        <v>256</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.6042649999999998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002904665979638735</v>
+        <v>0.6621400000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.005404442616958723</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2</v>
+        <v>0.59243595</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>0.005427562149575051</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.0003384522041201141</v>
       </c>
       <c r="F9" t="n">
-        <v>1024</v>
+        <v>0.95</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
         <v>128</v>
       </c>
-      <c r="I9" t="n">
-        <v>256</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>128</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.606115</v>
+      <c r="N9" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0004872420129560896</v>
+        <v>0.66064</v>
       </c>
       <c r="B10" t="n">
+        <v>0.007191870410400889</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.58760455</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.007115435537442585</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0003574712922600246</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="J10" t="n">
         <v>512</v>
       </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>10</v>
       </c>
-      <c r="H10" t="n">
+      <c r="L10" t="n">
+        <v>64</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64</v>
+      </c>
+      <c r="N10" t="n">
         <v>256</v>
-      </c>
-      <c r="I10" t="n">
-        <v>256</v>
-      </c>
-      <c r="J10" t="n">
-        <v>128</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5858949999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0001017364485544502</v>
+        <v>0.6604599999999999</v>
       </c>
       <c r="B11" t="n">
+        <v>0.00562832124172033</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.57821005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005781971972216741</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.002904665979638735</v>
+      </c>
+      <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
-        <v>512</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="n">
+      <c r="L11" t="n">
         <v>128</v>
       </c>
-      <c r="I11" t="n">
-        <v>64</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
+        <v>256</v>
+      </c>
+      <c r="N11" t="n">
         <v>128</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.60956</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0004841041099321571</v>
+        <v>0.6597799999999999</v>
       </c>
       <c r="B12" t="n">
+        <v>0.005766021158476614</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5693566499999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.005410817580897519</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0001972161097057403</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.95</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.5</v>
       </c>
-      <c r="F12" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
+        <v>512</v>
+      </c>
+      <c r="K12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
+      <c r="L12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M12" t="n">
+        <v>256</v>
+      </c>
+      <c r="N12" t="n">
         <v>128</v>
-      </c>
-      <c r="I12" t="n">
-        <v>256</v>
-      </c>
-      <c r="J12" t="n">
-        <v>128</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.5932999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0004135867955263891</v>
+        <v>0.65896</v>
       </c>
       <c r="B13" t="n">
+        <v>0.003054177467011373</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.60949705</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.00283461203474129</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0003571439909823144</v>
+      </c>
+      <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
+      <c r="G13" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>512</v>
-      </c>
-      <c r="G13" t="n">
-        <v>10</v>
-      </c>
       <c r="H13" t="n">
-        <v>64</v>
+        <v>0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>128</v>
+        <v>1024</v>
       </c>
       <c r="K13" t="n">
-        <v>0.668</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>0.577765</v>
+        <v>256</v>
+      </c>
+      <c r="M13" t="n">
+        <v>256</v>
+      </c>
+      <c r="N13" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002322119672134761</v>
+        <v>0.65748</v>
       </c>
       <c r="B14" t="n">
+        <v>0.003891914695879177</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5960015499999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.003354208850459432</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0008099164993582627</v>
+      </c>
+      <c r="F14" t="n">
         <v>0.9</v>
       </c>
-      <c r="C14" t="n">
+      <c r="G14" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4</v>
-      </c>
       <c r="H14" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="n">
+        <v>256</v>
+      </c>
+      <c r="M14" t="n">
+        <v>64</v>
+      </c>
+      <c r="N14" t="n">
         <v>128</v>
-      </c>
-      <c r="J14" t="n">
-        <v>256</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.600715</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.002458429052828939</v>
+        <v>0.65722</v>
       </c>
       <c r="B15" t="n">
-        <v>0.95</v>
+        <v>0.004078234912311944</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1</v>
+        <v>0.5787798000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05</v>
+        <v>0.003776002397542941</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.0009836162684900027</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>128</v>
+      </c>
+      <c r="M15" t="n">
         <v>256</v>
       </c>
-      <c r="I15" t="n">
+      <c r="N15" t="n">
         <v>128</v>
-      </c>
-      <c r="J15" t="n">
-        <v>256</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5836950000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0008099164993582627</v>
+        <v>0.6550799999999999</v>
       </c>
       <c r="B16" t="n">
+        <v>0.004020820811724913</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5714266</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.003804497858620726</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.002322119672134761</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.9</v>
       </c>
-      <c r="C16" t="n">
+      <c r="G16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G16" t="n">
-        <v>10</v>
-      </c>
       <c r="H16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>64</v>
+      </c>
+      <c r="M16" t="n">
+        <v>128</v>
+      </c>
+      <c r="N16" t="n">
         <v>256</v>
-      </c>
-      <c r="I16" t="n">
-        <v>64</v>
-      </c>
-      <c r="J16" t="n">
-        <v>128</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.6012999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0003571439909823144</v>
+        <v>0.65382</v>
       </c>
       <c r="B17" t="n">
+        <v>0.007384578525549026</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.58459395</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.007639983518879498</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0004135867955263891</v>
+      </c>
+      <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="G17" t="n">
         <v>0.1</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
       <c r="H17" t="n">
-        <v>256</v>
+        <v>0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>256</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="K17" t="n">
-        <v>0.648</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>0.58956</v>
+        <v>64</v>
+      </c>
+      <c r="M17" t="n">
+        <v>64</v>
+      </c>
+      <c r="N17" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0002139331892500008</v>
+        <v>0.6534799999999999</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.003921351807731608</v>
       </c>
       <c r="C18" t="n">
+        <v>0.5694732499999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.003362883542252117</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0004841041099321571</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.2</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="H18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.5</v>
       </c>
-      <c r="F18" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
-        <v>64</v>
-      </c>
-      <c r="I18" t="n">
-        <v>64</v>
-      </c>
-      <c r="J18" t="n">
-        <v>64</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.64</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.599205</v>
+        <v>128</v>
+      </c>
+      <c r="M18" t="n">
+        <v>256</v>
+      </c>
+      <c r="N18" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.0001942663440330811</v>
+        <v>0.6525399999999999</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9</v>
+        <v>0.005709027938274597</v>
       </c>
       <c r="C19" t="n">
+        <v>0.5536093500000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.005244797549119547</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.002190714227215282</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.3</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="H19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="F19" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>128</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
+        <v>64</v>
+      </c>
+      <c r="M19" t="n">
         <v>256</v>
       </c>
-      <c r="J19" t="n">
-        <v>64</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.6012900000000001</v>
+      <c r="N19" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.0003384522041201141</v>
+        <v>0.6515599999999999</v>
       </c>
       <c r="B20" t="n">
-        <v>0.95</v>
+        <v>0.002428579831918207</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1</v>
+        <v>0.5580386500000001</v>
       </c>
       <c r="D20" t="n">
+        <v>0.002752399757484346</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.002442046084491142</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.01</v>
       </c>
-      <c r="E20" t="n">
+      <c r="I20" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>64</v>
+      </c>
+      <c r="M20" t="n">
         <v>128</v>
       </c>
-      <c r="I20" t="n">
+      <c r="N20" t="n">
         <v>128</v>
-      </c>
-      <c r="J20" t="n">
-        <v>64</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.5481549999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.0001972161097057403</v>
+        <v>0.65062</v>
       </c>
       <c r="B21" t="n">
-        <v>0.95</v>
+        <v>0.007245826384892223</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1</v>
+        <v>0.5752075999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01</v>
+        <v>0.006587320323925353</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5</v>
+        <v>0.0001017364485544502</v>
       </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
         <v>512</v>
       </c>
-      <c r="G21" t="n">
+      <c r="K21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
-        <v>64</v>
-      </c>
-      <c r="I21" t="n">
-        <v>256</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>128</v>
       </c>
-      <c r="K21" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.55403</v>
+      <c r="M21" t="n">
+        <v>64</v>
+      </c>
+      <c r="N21" t="n">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2336,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.602185</v>
+        <v>0.59842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.68</v>
+        <v>0.656</v>
       </c>
       <c r="D2" t="n">
-        <v>9.324</v>
+        <v>8.282</v>
       </c>
     </row>
     <row r="3">
@@ -2350,13 +2930,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5773400000000001</v>
+        <v>0.58292</v>
       </c>
       <c r="C3" t="n">
-        <v>0.66</v>
+        <v>0.646</v>
       </c>
       <c r="D3" t="n">
-        <v>9.811999999999999</v>
+        <v>8.672000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2364,13 +2944,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.606115</v>
+        <v>0.602645</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="D4" t="n">
-        <v>9.545999999999999</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="5">
@@ -2378,13 +2958,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.574755</v>
+        <v>0.62909</v>
       </c>
       <c r="C5" t="n">
-        <v>0.654</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>9.26</v>
+        <v>8.646000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2392,13 +2972,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5856549999999999</v>
+        <v>0.6351750000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>0.676</v>
+        <v>0.696</v>
       </c>
       <c r="D6" t="n">
-        <v>10.486</v>
+        <v>8.516</v>
       </c>
     </row>
   </sheetData>
@@ -2442,13 +3022,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5934349999999999</v>
+        <v>0.63363</v>
       </c>
       <c r="C2" t="n">
-        <v>0.672</v>
+        <v>0.694</v>
       </c>
       <c r="D2" t="n">
-        <v>9.496</v>
+        <v>8.444000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2456,13 +3036,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.58701</v>
+        <v>0.632225</v>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>9.938000000000001</v>
+        <v>8.256</v>
       </c>
     </row>
     <row r="4">
@@ -2470,13 +3050,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.606115</v>
+        <v>0.602645</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="D4" t="n">
-        <v>9.545999999999999</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="5">
@@ -2484,13 +3064,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6255550000000001</v>
+        <v>0.6078450000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.71</v>
+        <v>0.668</v>
       </c>
       <c r="D5" t="n">
-        <v>9.972</v>
+        <v>8.448</v>
       </c>
     </row>
     <row r="6">
@@ -2498,13 +3078,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.577645</v>
+        <v>0.6320750000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>9.69</v>
+        <v>8.412000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2548,13 +3128,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6246700000000001</v>
+        <v>0.6846950000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.718</v>
+        <v>0.752</v>
       </c>
       <c r="D2" t="n">
-        <v>10.82</v>
+        <v>9.428000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2562,13 +3142,13 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.58636</v>
+        <v>0.60975</v>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.674</v>
       </c>
       <c r="D3" t="n">
-        <v>9.832000000000001</v>
+        <v>9.196</v>
       </c>
     </row>
     <row r="4">
@@ -2576,13 +3156,13 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.606115</v>
+        <v>0.602645</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="D4" t="n">
-        <v>9.545999999999999</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="5">
@@ -2590,13 +3170,13 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51484</v>
+        <v>0.578835</v>
       </c>
       <c r="C5" t="n">
-        <v>0.58</v>
+        <v>0.634</v>
       </c>
       <c r="D5" t="n">
-        <v>7.738</v>
+        <v>8.006</v>
       </c>
     </row>
     <row r="6">
@@ -2604,13 +3184,13 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.441815</v>
+        <v>0.51555</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>7.09</v>
+        <v>6.802</v>
       </c>
     </row>
   </sheetData>
